--- a/models/MNT-HALN-Valuation-Model.xlsx
+++ b/models/MNT-HALN-Valuation-Model.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Valuations\HALN - CA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Portfolio\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B6EAA8F-B806-4DB1-8850-971A56C1D749}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB07D556-316C-41C5-B6E9-173468F884A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="646" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1010,7 +1010,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-EGP 10-year government bond yield: Cbonds index 23.35% on 12 Oct 2026. Confirm against the latest Ministry of Finance 10-year auction before publishing.</t>
+EGP 10-year government bond yield: Cbonds index 23.35% on 12 Oct 2026.</t>
         </r>
       </text>
     </comment>
@@ -1058,65 +1058,7 @@
             <family val="2"/>
           </rPr>
           <t xml:space="preserve">
-5.0% = middle of a 4.5-5.5% mature-market (US implied) premium. Egypt country risk is already inside the EGP 10-year yield in C6, so Damodaran's total Egypt premium (13.94%) would count it twice. Update from Damodaran's latest monthly implied ERP and write the date here.</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="C21" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Ahmed Wael:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-"Industry" uses C23 as published; "Blume-adjusted" pulls it toward 1. HALN has no trading history yet (listing expected 20 Oct 2026), so there is no observed beta. Once peer or HALN betas exist, regress 104 weekly returns on the EGX30.</t>
-        </r>
-      </text>
-    </comment>
-  </commentList>
-</comments>
-</file>
-
-<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
-  <authors>
-    <author>Ahmed Wael</author>
-  </authors>
-  <commentList>
-    <comment ref="D36" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Ahmed Wael:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Book multiples on the two lenders only (Contact Financial, CI Capital). Fawry and e-finance are asset-light payment platforms; their P/B (8-10x) says nothing about a balance-sheet lender.</t>
+5.0% = middle of a 4.5-5.5% mature-market (US implied) premium. Egypt country risk is already inside the EGP 10-year yield in C6, so Damodaran's total Egypt premium (13.94%) would count it twice.</t>
         </r>
       </text>
     </comment>
@@ -2225,18 +2167,6 @@
     <t>PEER STATISTICS</t>
   </si>
   <si>
-    <t>P/E (all)</t>
-  </si>
-  <si>
-    <t>P/B (lenders)</t>
-  </si>
-  <si>
-    <t>P/TBV (lenders)</t>
-  </si>
-  <si>
-    <t>ROE (all)</t>
-  </si>
-  <si>
     <t>Mean</t>
   </si>
   <si>
@@ -2298,6 +2228,18 @@
   </si>
   <si>
     <t>USD/EGP</t>
+  </si>
+  <si>
+    <t>P/B</t>
+  </si>
+  <si>
+    <t>P/TBV</t>
+  </si>
+  <si>
+    <t>ROE</t>
+  </si>
+  <si>
+    <t>P/E</t>
   </si>
 </sst>
 </file>
@@ -14526,7 +14468,7 @@
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B32" s="284" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="C32" s="285">
         <f>D8</f>
@@ -14759,7 +14701,7 @@
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="201" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="C50" s="288">
         <f ca="1">C49/C51</f>
@@ -14775,7 +14717,7 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="C51" s="127">
         <v>50</v>
@@ -15222,7 +15164,7 @@
       <formula>#REF!="Industry"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
+  <dataValidations disablePrompts="1" count="1">
     <dataValidation type="list" sqref="C21" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"Industry,Blume-adjusted"</formula1>
     </dataValidation>
@@ -15234,7 +15176,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B1:I70"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -15758,16 +15700,16 @@
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C36" s="44" t="s">
-        <v>366</v>
+        <v>390</v>
       </c>
       <c r="D36" s="44" t="s">
-        <v>367</v>
+        <v>387</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>368</v>
+        <v>388</v>
       </c>
       <c r="F36" s="44" t="s">
-        <v>369</v>
+        <v>389</v>
       </c>
       <c r="G36" s="44"/>
     </row>
@@ -15780,19 +15722,19 @@
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B38" s="35" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="C38" s="149">
         <f>AVERAGE(C30:F30)</f>
         <v>19.345791137266943</v>
       </c>
       <c r="D38" s="149">
-        <f>AVERAGE(E31:F31)</f>
-        <v>1.2477779033630894</v>
+        <f>AVERAGE(C31:F31)</f>
+        <v>5.1052706414588993</v>
       </c>
       <c r="E38" s="149">
-        <f>AVERAGE(E32:F32)</f>
-        <v>1.304441547496455</v>
+        <f>AVERAGE(C32:F32)</f>
+        <v>5.7107200931403943</v>
       </c>
       <c r="F38" s="1">
         <f>AVERAGE(C33:F33)</f>
@@ -15802,19 +15744,19 @@
     </row>
     <row r="39" spans="2:7" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="44" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="C39" s="150">
         <f>MEDIAN(C30:F30)</f>
         <v>17.822519791535356</v>
       </c>
       <c r="D39" s="150">
-        <f>MEDIAN(E31:F31)</f>
-        <v>1.2477779033630894</v>
+        <f>MEDIAN(C31:F31)</f>
+        <v>4.8370113736834313</v>
       </c>
       <c r="E39" s="150">
-        <f>MEDIAN(E32:F32)</f>
-        <v>1.304441547496455</v>
+        <f>MEDIAN(C32:F32)</f>
+        <v>5.6980566128732537</v>
       </c>
       <c r="F39" s="167">
         <f>MEDIAN(C33:F33)</f>
@@ -15824,19 +15766,19 @@
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B40" s="35" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="C40" s="149">
         <f>MAX(C30:F30)</f>
         <v>34.732926313227686</v>
       </c>
       <c r="D40" s="149">
-        <f>MAX(E31:F31)</f>
-        <v>1.4337199699095724</v>
+        <f>MAX(C31:F31)</f>
+        <v>9.6852239816521308</v>
       </c>
       <c r="E40" s="149">
-        <f>MAX(E32:F32)</f>
-        <v>1.5196377063320523</v>
+        <f>MAX(C32:F32)</f>
+        <v>10.357521758154215</v>
       </c>
       <c r="F40" s="1">
         <f>MAX(C33:F33)</f>
@@ -15846,18 +15788,18 @@
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B41" s="35" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="C41" s="149">
         <f>MIN(C30:F30)</f>
         <v>7.0051986527693701</v>
       </c>
       <c r="D41" s="149">
-        <f>MIN(E31:F31)</f>
+        <f>MIN(C31:F31)</f>
         <v>1.0618358368166061</v>
       </c>
       <c r="E41" s="149">
-        <f>MIN(E32:F32)</f>
+        <f>MIN(C32:F32)</f>
         <v>1.089245388660858</v>
       </c>
       <c r="F41" s="1">
@@ -15868,7 +15810,7 @@
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B43" s="145" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="C43" s="146"/>
       <c r="D43" s="146"/>
@@ -15878,12 +15820,12 @@
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B44" s="44" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B45" s="35" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="C45" s="149">
         <f>C39</f>
@@ -15892,7 +15834,7 @@
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B46" s="35" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C46" s="151">
         <f>$G$23</f>
@@ -15901,7 +15843,7 @@
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B47" s="35" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C47" s="151">
         <f>C45*C46</f>
@@ -15919,7 +15861,7 @@
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="44" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C49" s="249">
         <f>C47/C48</f>
@@ -15928,21 +15870,21 @@
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="44" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="35" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="C52" s="149">
         <f>D39</f>
-        <v>1.2477779033630894</v>
+        <v>4.8370113736834313</v>
       </c>
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="35" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="C53" s="151">
         <f>G24</f>
@@ -15951,11 +15893,11 @@
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="35" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C54" s="151">
         <f>C52*C53</f>
-        <v>11374432050.214367</v>
+        <v>44092988862.671463</v>
       </c>
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
@@ -15969,11 +15911,11 @@
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="44" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C56" s="249">
         <f>C54/C55</f>
-        <v>7.1090200313839791</v>
+        <v>27.558118039169663</v>
       </c>
     </row>
     <row r="57" spans="2:3" x14ac:dyDescent="0.25">
@@ -15982,21 +15924,21 @@
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58" s="44" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59" s="35" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="C59" s="149">
         <f>E39</f>
-        <v>1.304441547496455</v>
+        <v>5.6980566128732537</v>
       </c>
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60" s="35" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="C60" s="151">
         <f>G27</f>
@@ -16005,11 +15947,11 @@
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61" s="35" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C61" s="151">
         <f>C59*C60</f>
-        <v>11186259613.377829</v>
+        <v>48863776752.325317</v>
       </c>
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
@@ -16023,21 +15965,21 @@
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63" s="44" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C63" s="249">
         <f>C61/C62</f>
-        <v>6.9914122583611427</v>
+        <v>30.539860470203323</v>
       </c>
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65" s="44" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66" s="35" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="C66" s="149">
         <f>MEDIAN(E30:F30)</f>
@@ -16046,7 +15988,7 @@
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67" s="35" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="C67" s="151">
         <f>G23</f>
@@ -16055,7 +15997,7 @@
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68" s="35" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="C68" s="151">
         <f>C66*C67</f>
@@ -16073,7 +16015,7 @@
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70" s="44" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="C70" s="249">
         <f>C68/C69</f>
@@ -16082,7 +16024,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 

--- a/models/MNT-HALN-Valuation-Model.xlsx
+++ b/models/MNT-HALN-Valuation-Model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Portfolio\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB07D556-316C-41C5-B6E9-173468F884A6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{27E2EAE6-9979-47EE-9BC7-74AE97497400}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="646" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,7 +59,7 @@
     <definedName name="IQ_YTD">3000</definedName>
     <definedName name="IQ_YTDMONTH" hidden="1">130000</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterate="1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1246,9 +1246,6 @@
     <t>Net diluted shares outstanding</t>
   </si>
   <si>
-    <t>Sensitivity - implied value (EGP): rows = cost of equity; columns = growth of residual income (columns only change the answer when D36 = 0). Centre cell = base case</t>
-  </si>
-  <si>
     <t>Company Name</t>
   </si>
   <si>
@@ -2197,18 +2194,12 @@
     <t>Implied value per share</t>
   </si>
   <si>
-    <t>Via Lender Median P/B:</t>
-  </si>
-  <si>
     <t>Peer median P/B</t>
   </si>
   <si>
     <t>x LTM book value of equity</t>
   </si>
   <si>
-    <t>Via Lender Median P/TBV:</t>
-  </si>
-  <si>
     <t>Peer Median P/TBV</t>
   </si>
   <si>
@@ -2240,6 +2231,15 @@
   </si>
   <si>
     <t>P/E</t>
+  </si>
+  <si>
+    <t>Sensitivity</t>
+  </si>
+  <si>
+    <t>Via Median P/TBV:</t>
+  </si>
+  <si>
+    <t>Via Median P/B:</t>
   </si>
 </sst>
 </file>
@@ -3744,23 +3744,23 @@
     <row r="4" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="5" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C5" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D5" s="168" t="s">
         <v>60</v>
-      </c>
-      <c r="D5" s="168" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="6" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="D6" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="7" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C7" s="6" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D7" s="129">
         <v>24.5</v>
@@ -3768,7 +3768,7 @@
     </row>
     <row r="8" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C8" s="6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D8" s="5">
         <v>46302</v>
@@ -3776,7 +3776,7 @@
     </row>
     <row r="9" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C9" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D9" s="5">
         <v>46022</v>
@@ -3793,7 +3793,7 @@
     <row r="11" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C12" s="38" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D12" s="95"/>
       <c r="E12" s="39"/>
@@ -3806,7 +3806,7 @@
     </row>
     <row r="13" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D13" s="40">
         <f>E13-1</f>
@@ -3843,7 +3843,7 @@
     </row>
     <row r="14" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C14" s="42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D14" s="86">
         <f>EOMONTH(E14,-12)</f>
@@ -3881,7 +3881,7 @@
     <row r="15" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="16" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C16" s="6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D16" s="152">
         <v>7607109195</v>
@@ -3915,7 +3915,7 @@
     </row>
     <row r="17" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C17" s="6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D17" s="152">
         <v>1805005316</v>
@@ -3949,7 +3949,7 @@
     </row>
     <row r="18" spans="3:11" s="134" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C18" s="133" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D18" s="153">
         <f t="shared" ref="D18:K18" si="0">SUM(D16:D17)</f>
@@ -3986,7 +3986,7 @@
     </row>
     <row r="19" spans="3:11" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C19" s="84" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D19" s="152">
         <v>-2239890778</v>
@@ -3998,29 +3998,29 @@
         <v>-6963884903</v>
       </c>
       <c r="G19" s="158">
-        <f t="shared" ref="G19:K20" ca="1" si="1">-G193</f>
-        <v>-6756494037.6363268</v>
+        <f t="shared" ref="G19:K20" si="1">-G193</f>
+        <v>-6568239919.2325459</v>
       </c>
       <c r="H19" s="158">
-        <f t="shared" ca="1" si="1"/>
-        <v>-7218772371.2625799</v>
+        <f t="shared" si="1"/>
+        <v>-6858864679.4139566</v>
       </c>
       <c r="I19" s="158">
-        <f t="shared" ca="1" si="1"/>
-        <v>-7780036844.0131531</v>
+        <f t="shared" si="1"/>
+        <v>-7416760639.4370899</v>
       </c>
       <c r="J19" s="158">
-        <f t="shared" ca="1" si="1"/>
-        <v>-8182903054.4936485</v>
+        <f t="shared" si="1"/>
+        <v>-7872220495.6001749</v>
       </c>
       <c r="K19" s="158">
-        <f t="shared" ca="1" si="1"/>
-        <v>-8426897780.7023354</v>
+        <f t="shared" si="1"/>
+        <v>-8136375388.8221512</v>
       </c>
     </row>
     <row r="20" spans="3:11" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C20" s="84" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D20" s="152">
         <v>-1812939327</v>
@@ -4054,7 +4054,7 @@
     </row>
     <row r="21" spans="3:11" s="157" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C21" s="156" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D21" s="153">
         <f t="shared" ref="D21:K21" si="2">SUM(D19:D20)</f>
@@ -4069,29 +4069,29 @@
         <v>-8941506786</v>
       </c>
       <c r="G21" s="153">
-        <f t="shared" ca="1" si="2"/>
-        <v>-8832997014.7863274</v>
+        <f t="shared" si="2"/>
+        <v>-8644742896.3825455</v>
       </c>
       <c r="H21" s="153">
-        <f t="shared" ca="1" si="2"/>
-        <v>-9399100497.2700806</v>
+        <f t="shared" si="2"/>
+        <v>-9039192805.4214573</v>
       </c>
       <c r="I21" s="153">
-        <f t="shared" ca="1" si="2"/>
-        <v>-10069381376.321028</v>
+        <f t="shared" si="2"/>
+        <v>-9706105171.7449646</v>
       </c>
       <c r="J21" s="153">
-        <f t="shared" ca="1" si="2"/>
-        <v>-10586714813.416918</v>
+        <f t="shared" si="2"/>
+        <v>-10276032254.523443</v>
       </c>
       <c r="K21" s="153">
-        <f t="shared" ca="1" si="2"/>
-        <v>-10950900127.571768</v>
+        <f t="shared" si="2"/>
+        <v>-10660377735.691584</v>
       </c>
     </row>
     <row r="22" spans="3:11" s="157" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C22" s="156" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D22" s="153">
         <f t="shared" ref="D22:K22" si="3">D18+D21</f>
@@ -4106,29 +4106,29 @@
         <v>10868977382</v>
       </c>
       <c r="G22" s="153">
-        <f t="shared" ca="1" si="3"/>
-        <v>10665266797.289104</v>
+        <f t="shared" si="3"/>
+        <v>10853520915.692886</v>
       </c>
       <c r="H22" s="153">
-        <f t="shared" ca="1" si="3"/>
-        <v>12357040611.006367</v>
+        <f t="shared" si="3"/>
+        <v>12716948302.85499</v>
       </c>
       <c r="I22" s="153">
-        <f t="shared" ca="1" si="3"/>
-        <v>13912396106.792265</v>
+        <f t="shared" si="3"/>
+        <v>14275672311.368328</v>
       </c>
       <c r="J22" s="153">
-        <f t="shared" ca="1" si="3"/>
-        <v>15448923338.453474</v>
+        <f t="shared" si="3"/>
+        <v>15759605897.346949</v>
       </c>
       <c r="K22" s="153">
-        <f t="shared" ca="1" si="3"/>
-        <v>17151015059.477877</v>
+        <f t="shared" si="3"/>
+        <v>17441537451.358063</v>
       </c>
     </row>
     <row r="23" spans="3:11" s="157" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C23" s="156" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D23" s="153">
         <f t="shared" ref="D23:K23" si="4">D49</f>
@@ -4165,7 +4165,7 @@
     </row>
     <row r="24" spans="3:11" s="157" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C24" s="156" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D24" s="153">
         <f t="shared" ref="D24:K24" si="5">SUM(D22:D23)</f>
@@ -4180,29 +4180,29 @@
         <v>2606222609</v>
       </c>
       <c r="G24" s="153">
-        <f t="shared" ca="1" si="5"/>
-        <v>2674867909.9132538</v>
+        <f t="shared" si="5"/>
+        <v>2863122028.3170357</v>
       </c>
       <c r="H24" s="153">
-        <f t="shared" ca="1" si="5"/>
-        <v>3427604794.7684288</v>
+        <f t="shared" si="5"/>
+        <v>3787512486.6170521</v>
       </c>
       <c r="I24" s="153">
-        <f t="shared" ca="1" si="5"/>
-        <v>4046791071.0476151</v>
+        <f t="shared" si="5"/>
+        <v>4410067275.6236782</v>
       </c>
       <c r="J24" s="153">
-        <f t="shared" ca="1" si="5"/>
-        <v>4710798488.4195137</v>
+        <f t="shared" si="5"/>
+        <v>5021481047.3129883</v>
       </c>
       <c r="K24" s="153">
-        <f t="shared" ca="1" si="5"/>
-        <v>5552008524.9906769</v>
+        <f t="shared" si="5"/>
+        <v>5842530916.870863</v>
       </c>
     </row>
     <row r="25" spans="3:11" s="15" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C25" s="84" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D25" s="155">
         <v>-148645274</v>
@@ -4236,7 +4236,7 @@
     </row>
     <row r="26" spans="3:11" s="134" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C26" s="133" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D26" s="153">
         <f t="shared" ref="D26:K26" si="6">SUM(D24:D25)</f>
@@ -4251,29 +4251,29 @@
         <v>2312525202</v>
       </c>
       <c r="G26" s="153">
-        <f t="shared" ca="1" si="6"/>
-        <v>2178760541.5332308</v>
+        <f t="shared" si="6"/>
+        <v>2367014659.9370127</v>
       </c>
       <c r="H26" s="153">
-        <f t="shared" ca="1" si="6"/>
-        <v>2836284835.2563505</v>
+        <f t="shared" si="6"/>
+        <v>3196192527.1049738</v>
       </c>
       <c r="I26" s="153">
-        <f t="shared" ca="1" si="6"/>
-        <v>3355320860.3290033</v>
+        <f t="shared" si="6"/>
+        <v>3718597064.9050665</v>
       </c>
       <c r="J26" s="153">
-        <f t="shared" ca="1" si="6"/>
-        <v>3915254948.5427637</v>
+        <f t="shared" si="6"/>
+        <v>4225937507.4362383</v>
       </c>
       <c r="K26" s="153">
-        <f t="shared" ca="1" si="6"/>
-        <v>4650414245.8056421</v>
+        <f t="shared" si="6"/>
+        <v>4940936637.6858282</v>
       </c>
     </row>
     <row r="27" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C27" s="85" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D27" s="152">
         <v>299357186</v>
@@ -4285,29 +4285,29 @@
         <v>655970125</v>
       </c>
       <c r="G27" s="110">
-        <f ca="1">G236</f>
-        <v>766975786.49670184</v>
+        <f>G236</f>
+        <v>787070974.42444801</v>
       </c>
       <c r="H27" s="110">
-        <f ca="1">H236</f>
-        <v>780868468.42743003</v>
+        <f>H236</f>
+        <v>742065465.77015889</v>
       </c>
       <c r="I27" s="110">
-        <f ca="1">I236</f>
-        <v>857762863.29723787</v>
+        <f>I236</f>
+        <v>818956544.85617316</v>
       </c>
       <c r="J27" s="110">
-        <f ca="1">J236</f>
-        <v>929104295.37221551</v>
+        <f>J236</f>
+        <v>894303181.76039219</v>
       </c>
       <c r="K27" s="110">
-        <f ca="1">K236</f>
-        <v>996554035.14182258</v>
+        <f>K236</f>
+        <v>960111573.10477364</v>
       </c>
     </row>
     <row r="28" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C28" s="85" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D28" s="152">
         <v>-111537468</v>
@@ -4341,7 +4341,7 @@
     </row>
     <row r="29" spans="3:11" s="44" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C29" s="135" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D29" s="153">
         <f t="shared" ref="D29:K29" si="7">SUM(D27:D28)</f>
@@ -4356,29 +4356,29 @@
         <v>508432272</v>
       </c>
       <c r="G29" s="153">
-        <f t="shared" ca="1" si="7"/>
-        <v>622427255.93919015</v>
+        <f t="shared" si="7"/>
+        <v>642522443.86693633</v>
       </c>
       <c r="H29" s="153">
-        <f t="shared" ca="1" si="7"/>
-        <v>622741312.30313659</v>
+        <f t="shared" si="7"/>
+        <v>583938309.64586544</v>
       </c>
       <c r="I29" s="153">
-        <f t="shared" ca="1" si="7"/>
-        <v>684071525.97205484</v>
+        <f t="shared" si="7"/>
+        <v>645265207.53099012</v>
       </c>
       <c r="J29" s="153">
-        <f t="shared" ca="1" si="7"/>
-        <v>738176539.65210795</v>
+        <f t="shared" si="7"/>
+        <v>703375426.04028463</v>
       </c>
       <c r="K29" s="153">
-        <f t="shared" ca="1" si="7"/>
-        <v>787222400.64174545</v>
+        <f t="shared" si="7"/>
+        <v>750779938.60469651</v>
       </c>
     </row>
     <row r="30" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C30" s="85" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D30" s="152">
         <v>13023424</v>
@@ -4412,7 +4412,7 @@
     </row>
     <row r="31" spans="3:11" s="35" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C31" s="135" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D31" s="153">
         <f t="shared" ref="D31:K31" si="8">D26+SUM(D29:D30)</f>
@@ -4427,29 +4427,29 @@
         <v>2820957474</v>
       </c>
       <c r="G31" s="153">
-        <f t="shared" ca="1" si="8"/>
-        <v>2801187797.4724207</v>
+        <f t="shared" si="8"/>
+        <v>3009537103.8039489</v>
       </c>
       <c r="H31" s="153">
-        <f t="shared" ca="1" si="8"/>
-        <v>3459026147.5594873</v>
+        <f t="shared" si="8"/>
+        <v>3780130836.7508392</v>
       </c>
       <c r="I31" s="153">
-        <f t="shared" ca="1" si="8"/>
-        <v>4039392386.3010583</v>
+        <f t="shared" si="8"/>
+        <v>4363862272.4360561</v>
       </c>
       <c r="J31" s="153">
-        <f t="shared" ca="1" si="8"/>
-        <v>4653431488.1948719</v>
+        <f t="shared" si="8"/>
+        <v>4929312933.4765224</v>
       </c>
       <c r="K31" s="153">
-        <f t="shared" ca="1" si="8"/>
-        <v>5437636646.4473877</v>
+        <f t="shared" si="8"/>
+        <v>5691716576.2905245</v>
       </c>
     </row>
     <row r="32" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C32" s="6" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D32" s="152">
         <v>-674314071</v>
@@ -4461,29 +4461,29 @@
         <v>-862455085</v>
       </c>
       <c r="G32" s="59">
-        <f ca="1">-G40*G31</f>
-        <v>-784332583.29227781</v>
+        <f>-G40*G31</f>
+        <v>-842670389.0651058</v>
       </c>
       <c r="H32" s="59">
-        <f ca="1">-H40*H31</f>
-        <v>-968527321.31665659</v>
+        <f>-H40*H31</f>
+        <v>-1058436634.290235</v>
       </c>
       <c r="I32" s="59">
-        <f ca="1">-I40*I31</f>
-        <v>-1131029868.1642964</v>
+        <f>-I40*I31</f>
+        <v>-1221881436.2820959</v>
       </c>
       <c r="J32" s="59">
-        <f ca="1">-J40*J31</f>
-        <v>-1302960816.6945643</v>
+        <f>-J40*J31</f>
+        <v>-1380207621.3734264</v>
       </c>
       <c r="K32" s="59">
-        <f ca="1">-K40*K31</f>
-        <v>-1522538261.0052688</v>
+        <f>-K40*K31</f>
+        <v>-1593680641.361347</v>
       </c>
     </row>
     <row r="33" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C33" s="6" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D33" s="152">
         <v>-12294587</v>
@@ -4512,7 +4512,7 @@
     </row>
     <row r="34" spans="3:11" s="44" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C34" s="44" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D34" s="153">
         <f t="shared" ref="D34:K34" si="9">SUM(D31:D33)</f>
@@ -4527,29 +4527,29 @@
         <v>1978398739</v>
       </c>
       <c r="G34" s="153">
-        <f t="shared" ca="1" si="9"/>
-        <v>2016855214.1801429</v>
+        <f t="shared" si="9"/>
+        <v>2166866714.738843</v>
       </c>
       <c r="H34" s="153">
-        <f t="shared" ca="1" si="9"/>
-        <v>2490498826.2428308</v>
+        <f t="shared" si="9"/>
+        <v>2721694202.4606042</v>
       </c>
       <c r="I34" s="153">
-        <f t="shared" ca="1" si="9"/>
-        <v>2908362518.1367617</v>
+        <f t="shared" si="9"/>
+        <v>3141980836.1539602</v>
       </c>
       <c r="J34" s="153">
-        <f t="shared" ca="1" si="9"/>
-        <v>3350470671.5003076</v>
+        <f t="shared" si="9"/>
+        <v>3549105312.103096</v>
       </c>
       <c r="K34" s="153">
-        <f t="shared" ca="1" si="9"/>
-        <v>3915098385.4421186</v>
+        <f t="shared" si="9"/>
+        <v>4098035934.9291773</v>
       </c>
     </row>
     <row r="35" spans="3:11" s="35" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C35" s="35" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D35" s="154">
         <f t="shared" ref="D35:K35" si="10">D34-D36</f>
@@ -4564,29 +4564,29 @@
         <v>2018397923</v>
       </c>
       <c r="G35" s="154">
-        <f t="shared" ca="1" si="10"/>
-        <v>2016855214.1801429</v>
+        <f t="shared" si="10"/>
+        <v>2166866714.738843</v>
       </c>
       <c r="H35" s="154">
-        <f t="shared" ca="1" si="10"/>
-        <v>2490498826.2428308</v>
+        <f t="shared" si="10"/>
+        <v>2721694202.4606042</v>
       </c>
       <c r="I35" s="154">
-        <f t="shared" ca="1" si="10"/>
-        <v>2908362518.1367617</v>
+        <f t="shared" si="10"/>
+        <v>3141980836.1539602</v>
       </c>
       <c r="J35" s="154">
-        <f t="shared" ca="1" si="10"/>
-        <v>3350470671.5003076</v>
+        <f t="shared" si="10"/>
+        <v>3549105312.103096</v>
       </c>
       <c r="K35" s="154">
-        <f t="shared" ca="1" si="10"/>
-        <v>3915098385.4421186</v>
+        <f t="shared" si="10"/>
+        <v>4098035934.9291773</v>
       </c>
     </row>
     <row r="36" spans="3:11" s="35" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C36" s="35" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D36" s="155">
         <v>25557586</v>
@@ -4598,23 +4598,23 @@
         <v>-39999184</v>
       </c>
       <c r="G36" s="132">
-        <f ca="1">G251</f>
+        <f>G251</f>
         <v>0</v>
       </c>
       <c r="H36" s="132">
-        <f ca="1">H251</f>
+        <f>H251</f>
         <v>0</v>
       </c>
       <c r="I36" s="132">
-        <f ca="1">I251</f>
+        <f>I251</f>
         <v>0</v>
       </c>
       <c r="J36" s="132">
-        <f ca="1">J251</f>
+        <f>J251</f>
         <v>0</v>
       </c>
       <c r="K36" s="132">
-        <f ca="1">K251</f>
+        <f>K251</f>
         <v>0</v>
       </c>
     </row>
@@ -4631,7 +4631,7 @@
     </row>
     <row r="38" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C38" s="20" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D38" s="21"/>
       <c r="E38" s="21"/>
@@ -4643,7 +4643,7 @@
     </row>
     <row r="39" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C39" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D39" s="75"/>
       <c r="E39" s="75">
@@ -4677,7 +4677,7 @@
     </row>
     <row r="40" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C40" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D40" s="76">
         <f>-SUM(D32:D33)/D31</f>
@@ -4724,7 +4724,7 @@
     </row>
     <row r="42" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C42" s="38" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D42" s="96"/>
       <c r="E42" s="45"/>
@@ -4737,7 +4737,7 @@
     </row>
     <row r="43" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C43" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D43" s="40">
         <f t="shared" ref="D43:K43" si="12">D$13</f>
@@ -4774,7 +4774,7 @@
     </row>
     <row r="44" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C44" s="42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D44" s="86">
         <f t="shared" ref="D44:K44" si="13">D$14</f>
@@ -4822,7 +4822,7 @@
     </row>
     <row r="46" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C46" s="85" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D46" s="61">
         <v>-2664207469</v>
@@ -4856,7 +4856,7 @@
     </row>
     <row r="47" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C47" s="85" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D47" s="61">
         <v>-272561217</v>
@@ -4890,7 +4890,7 @@
     </row>
     <row r="48" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C48" s="85" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D48" s="61">
         <v>478498730</v>
@@ -4924,7 +4924,7 @@
     </row>
     <row r="49" spans="3:11" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C49" s="63" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D49" s="14">
         <f t="shared" ref="D49:K49" si="14">SUM(D46:D48)</f>
@@ -5091,7 +5091,7 @@
     </row>
     <row r="55" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C55" s="38" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D55" s="96"/>
       <c r="E55" s="45"/>
@@ -5104,7 +5104,7 @@
     </row>
     <row r="56" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C56" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D56" s="40">
         <f t="shared" ref="D56:K56" si="16">D$13</f>
@@ -5141,7 +5141,7 @@
     </row>
     <row r="57" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C57" s="42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D57" s="86">
         <f t="shared" ref="D57:K57" si="17">D$14</f>
@@ -5178,18 +5178,18 @@
     </row>
     <row r="58" spans="3:11" s="35" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C58" s="44" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="59" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="60" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C60" s="13" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="61" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C61" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D61" s="10">
         <v>392605602</v>
@@ -5223,7 +5223,7 @@
     </row>
     <row r="62" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C62" s="17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D62" s="10">
         <v>1100040440</v>
@@ -5257,7 +5257,7 @@
     </row>
     <row r="63" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C63" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D63" s="10">
         <v>234861219</v>
@@ -5291,7 +5291,7 @@
     </row>
     <row r="64" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C64" s="17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D64" s="10">
         <v>315405416</v>
@@ -5325,7 +5325,7 @@
     </row>
     <row r="65" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C65" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D65" s="10">
         <v>12313185015</v>
@@ -5359,7 +5359,7 @@
     </row>
     <row r="66" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C66" s="17" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D66" s="10">
         <v>1036009737</v>
@@ -5371,29 +5371,29 @@
         <v>3458917393</v>
       </c>
       <c r="G66" s="19">
-        <f ca="1">G146</f>
+        <f>G146</f>
         <v>1866746452.704</v>
       </c>
       <c r="H66" s="19">
-        <f ca="1">H146</f>
-        <v>1937135695.5864532</v>
+        <f>H146</f>
+        <v>1927536968.2271404</v>
       </c>
       <c r="I66" s="19">
-        <f ca="1">I146</f>
-        <v>2053187377.6247032</v>
+        <f>I146</f>
+        <v>2032362384.1632543</v>
       </c>
       <c r="J66" s="19">
-        <f ca="1">J146</f>
-        <v>2148052375.4771013</v>
+        <f>J146</f>
+        <v>2117940650.1584382</v>
       </c>
       <c r="K66" s="19">
-        <f ca="1">K146</f>
-        <v>2204579827.4946489</v>
+        <f>K146</f>
+        <v>2167573822.896246</v>
       </c>
     </row>
     <row r="67" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C67" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D67" s="12">
         <f t="shared" ref="D67:K67" si="19">SUM(D61:D66)</f>
@@ -5408,24 +5408,24 @@
         <v>29493590254</v>
       </c>
       <c r="G67" s="12">
-        <f t="shared" ca="1" si="19"/>
+        <f t="shared" si="19"/>
         <v>31179458024.110714</v>
       </c>
       <c r="H67" s="12">
-        <f t="shared" ca="1" si="19"/>
-        <v>34714838291.497269</v>
+        <f t="shared" si="19"/>
+        <v>34705239564.137955</v>
       </c>
       <c r="I67" s="12">
-        <f t="shared" ca="1" si="19"/>
-        <v>38144898842.26635</v>
+        <f t="shared" si="19"/>
+        <v>38124073848.804901</v>
       </c>
       <c r="J67" s="12">
-        <f t="shared" ca="1" si="19"/>
-        <v>41224644065.461021</v>
+        <f t="shared" si="19"/>
+        <v>41194532340.142357</v>
       </c>
       <c r="K67" s="12">
-        <f t="shared" ca="1" si="19"/>
-        <v>44373250523.682365</v>
+        <f t="shared" si="19"/>
+        <v>44336244519.083961</v>
       </c>
     </row>
     <row r="68" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5439,7 +5439,7 @@
     </row>
     <row r="69" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C69" s="13" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="E69" s="18"/>
       <c r="F69" s="18"/>
@@ -5451,7 +5451,7 @@
     </row>
     <row r="70" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C70" s="24" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D70" s="10">
         <v>890802394</v>
@@ -5485,7 +5485,7 @@
     </row>
     <row r="71" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C71" s="17" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D71" s="10">
         <v>385138334</v>
@@ -5519,7 +5519,7 @@
     </row>
     <row r="72" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C72" s="17" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D72" s="10">
         <v>69714128</v>
@@ -5553,7 +5553,7 @@
     </row>
     <row r="73" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C73" s="17" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D73" s="10">
         <v>21701220</v>
@@ -5587,7 +5587,7 @@
     </row>
     <row r="74" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C74" s="17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D74" s="10">
         <v>7041343295</v>
@@ -5621,7 +5621,7 @@
     </row>
     <row r="75" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C75" s="17" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D75" s="10">
         <v>170265786</v>
@@ -5655,7 +5655,7 @@
     </row>
     <row r="76" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C76" s="17" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D76" s="10">
         <v>15758360</v>
@@ -5689,7 +5689,7 @@
     </row>
     <row r="77" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C77" s="17" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D77" s="10">
         <v>31145974</v>
@@ -5723,7 +5723,7 @@
     </row>
     <row r="78" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C78" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D78" s="12">
         <f t="shared" ref="D78:K78" si="21">SUM(D70:D77)</f>
@@ -5769,7 +5769,7 @@
     </row>
     <row r="80" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C80" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D80" s="14">
         <f t="shared" ref="D80:K80" si="22">D67+D78</f>
@@ -5784,24 +5784,24 @@
         <v>41334187181</v>
       </c>
       <c r="G80" s="14">
-        <f t="shared" ca="1" si="22"/>
+        <f t="shared" si="22"/>
         <v>44735419438.889328</v>
       </c>
       <c r="H80" s="14">
-        <f t="shared" ca="1" si="22"/>
-        <v>50049504479.092072</v>
+        <f t="shared" si="22"/>
+        <v>50039905751.732758</v>
       </c>
       <c r="I80" s="14">
-        <f t="shared" ca="1" si="22"/>
-        <v>55228548037.015503</v>
+        <f t="shared" si="22"/>
+        <v>55207723043.554054</v>
       </c>
       <c r="J80" s="14">
-        <f t="shared" ca="1" si="22"/>
-        <v>59948501903.324081</v>
+        <f t="shared" si="22"/>
+        <v>59918390178.005417</v>
       </c>
       <c r="K80" s="14">
-        <f t="shared" ca="1" si="22"/>
-        <v>64761021303.646744</v>
+        <f t="shared" si="22"/>
+        <v>64724015299.04834</v>
       </c>
     </row>
     <row r="81" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5815,7 +5815,7 @@
     </row>
     <row r="82" spans="3:12" s="35" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C82" s="44" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D82" s="97"/>
       <c r="E82" s="46"/>
@@ -5837,7 +5837,7 @@
     </row>
     <row r="84" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C84" s="13" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="E84" s="18"/>
       <c r="F84" s="18"/>
@@ -5849,7 +5849,7 @@
     </row>
     <row r="85" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C85" s="17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D85" s="10">
         <v>7407591557</v>
@@ -5861,29 +5861,29 @@
         <v>9471234839</v>
       </c>
       <c r="G85" s="19">
-        <f ca="1">G315*G320</f>
-        <v>10887344320.429308</v>
+        <f>G315*G320</f>
+        <v>10805695531.957373</v>
       </c>
       <c r="H85" s="19">
-        <f ca="1">H315*H320</f>
-        <v>11874504272.353569</v>
+        <f>H315*H320</f>
+        <v>11697362509.449596</v>
       </c>
       <c r="I85" s="19">
-        <f ca="1">I315*I320</f>
-        <v>12838050769.602369</v>
+        <f>I315*I320</f>
+        <v>12581914117.415535</v>
       </c>
       <c r="J85" s="19">
-        <f ca="1">J315*J320</f>
-        <v>13318885134.395563</v>
+        <f>J315*J320</f>
+        <v>13004104296.421768</v>
       </c>
       <c r="K85" s="19">
-        <f ca="1">K315*K320</f>
-        <v>13617988448.425213</v>
+        <f>K315*K320</f>
+        <v>13246091180.976873</v>
       </c>
     </row>
     <row r="86" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C86" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D86" s="10">
         <v>0</v>
@@ -5916,7 +5916,7 @@
     </row>
     <row r="87" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C87" s="17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D87" s="10">
         <v>676644242</v>
@@ -5928,29 +5928,29 @@
         <v>867166386</v>
       </c>
       <c r="G87" s="19">
-        <f ca="1">-G32*(F87/-F32)</f>
-        <v>788617127.436391</v>
+        <f>-G32*(F87/-F32)</f>
+        <v>847273612.94971275</v>
       </c>
       <c r="H87" s="19">
-        <f ca="1">-H32*(G87/-G32)</f>
-        <v>973818059.13803124</v>
+        <f>-H32*(G87/-G32)</f>
+        <v>1064218516.3386992</v>
       </c>
       <c r="I87" s="19">
-        <f ca="1">-I32*(H87/-H32)</f>
-        <v>1137208302.5449252</v>
+        <f>-I32*(H87/-H32)</f>
+        <v>1228556162.1116006</v>
       </c>
       <c r="J87" s="19">
-        <f ca="1">-J32*(I87/-I32)</f>
-        <v>1310078451.8101993</v>
+        <f>-J32*(I87/-I32)</f>
+        <v>1387747229.7076786</v>
       </c>
       <c r="K87" s="19">
-        <f ca="1">-K32*(J87/-J32)</f>
-        <v>1530855373.5788612</v>
+        <f>-K32*(J87/-J32)</f>
+        <v>1602386380.7440839</v>
       </c>
     </row>
     <row r="88" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C88" s="17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D88" s="10">
         <v>689469467</v>
@@ -5984,7 +5984,7 @@
     </row>
     <row r="89" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C89" s="17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D89" s="10">
         <v>31158839</v>
@@ -6018,7 +6018,7 @@
     </row>
     <row r="90" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C90" s="17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D90" s="10">
         <v>164022527</v>
@@ -6052,7 +6052,7 @@
     </row>
     <row r="91" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C91" s="17" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D91" s="10">
         <v>40679260</v>
@@ -6086,7 +6086,7 @@
     </row>
     <row r="92" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C92" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D92" s="12">
         <f t="shared" ref="D92:K92" si="24">SUM(D85:D91)</f>
@@ -6101,24 +6101,24 @@
         <v>15723073385</v>
       </c>
       <c r="G92" s="12">
-        <f t="shared" ca="1" si="24"/>
-        <v>15093670770.187632</v>
+        <f t="shared" si="24"/>
+        <v>15070678467.229017</v>
       </c>
       <c r="H92" s="12">
-        <f t="shared" ca="1" si="24"/>
-        <v>16946299156.279848</v>
+        <f t="shared" si="24"/>
+        <v>16859557850.576544</v>
       </c>
       <c r="I92" s="12">
-        <f t="shared" ca="1" si="24"/>
-        <v>17949744704.855293</v>
+        <f t="shared" si="24"/>
+        <v>17784955912.235138</v>
       </c>
       <c r="J92" s="12">
-        <f t="shared" ca="1" si="24"/>
-        <v>18863089733.353329</v>
+        <f t="shared" si="24"/>
+        <v>18625977673.277012</v>
       </c>
       <c r="K92" s="12">
-        <f t="shared" ca="1" si="24"/>
-        <v>19652384429.551559</v>
+        <f t="shared" si="24"/>
+        <v>19352018169.268444</v>
       </c>
       <c r="L92" s="18"/>
     </row>
@@ -6134,7 +6134,7 @@
     </row>
     <row r="94" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C94" s="13" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E94" s="18"/>
       <c r="F94" s="18"/>
@@ -6146,7 +6146,7 @@
     </row>
     <row r="95" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C95" s="17" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D95" s="10">
         <v>7048011003</v>
@@ -6158,29 +6158,29 @@
         <v>14734188615</v>
       </c>
       <c r="G95" s="19">
-        <f ca="1">G315*(1-G320)</f>
-        <v>16937198523.797941</v>
+        <f>G315*(1-G320)</f>
+        <v>16810179326.197855</v>
       </c>
       <c r="H95" s="19">
-        <f ca="1">H315*(1-H320)</f>
-        <v>18472901224.879112</v>
+        <f>H315*(1-H320)</f>
+        <v>18197325738.621151</v>
       </c>
       <c r="I95" s="19">
-        <f ca="1">I315*(1-I320)</f>
-        <v>19971869001.638977</v>
+        <f>I315*(1-I320)</f>
+        <v>19573402929.507038</v>
       </c>
       <c r="J95" s="19">
-        <f ca="1">J315*(1-J320)</f>
-        <v>20719892289.401176</v>
+        <f>J315*(1-J320)</f>
+        <v>20230194766.540112</v>
       </c>
       <c r="K95" s="19">
-        <f ca="1">K315*(1-K320)</f>
-        <v>21185200638.227814</v>
+        <f>K315*(1-K320)</f>
+        <v>20606648361.029129</v>
       </c>
     </row>
     <row r="96" spans="3:12" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C96" s="17" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D96" s="10">
         <v>0</v>
@@ -6214,7 +6214,7 @@
     </row>
     <row r="97" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C97" s="17" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="D97" s="10">
         <v>62631706</v>
@@ -6248,7 +6248,7 @@
     </row>
     <row r="98" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C98" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D98" s="10">
         <v>648058235</v>
@@ -6282,7 +6282,7 @@
     </row>
     <row r="99" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C99" s="17" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D99" s="10">
         <v>665607751</v>
@@ -6316,7 +6316,7 @@
     </row>
     <row r="100" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C100" s="11" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D100" s="12">
         <f t="shared" ref="D100:K100" si="25">SUM(D95:D99)</f>
@@ -6331,24 +6331,24 @@
         <v>16500914386</v>
       </c>
       <c r="G100" s="12">
-        <f t="shared" ca="1" si="25"/>
-        <v>18767985584.522346</v>
+        <f t="shared" si="25"/>
+        <v>18640966386.922256</v>
       </c>
       <c r="H100" s="12">
-        <f t="shared" ca="1" si="25"/>
-        <v>19976885325.013561</v>
+        <f t="shared" si="25"/>
+        <v>19701309838.7556</v>
       </c>
       <c r="I100" s="12">
-        <f t="shared" ca="1" si="25"/>
-        <v>21557171139.97823</v>
+        <f t="shared" si="25"/>
+        <v>21158705067.846291</v>
       </c>
       <c r="J100" s="12">
-        <f t="shared" ca="1" si="25"/>
-        <v>22392020314.850876</v>
+        <f t="shared" si="25"/>
+        <v>21902322791.989811</v>
       </c>
       <c r="K100" s="12">
-        <f t="shared" ca="1" si="25"/>
-        <v>22949039814.771389</v>
+        <f t="shared" si="25"/>
+        <v>22370487537.572704</v>
       </c>
     </row>
     <row r="101" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6363,7 +6363,7 @@
     </row>
     <row r="102" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C102" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="D102" s="25">
         <f t="shared" ref="D102:K102" si="26">D92+D100</f>
@@ -6378,24 +6378,24 @@
         <v>32223987771</v>
       </c>
       <c r="G102" s="25">
-        <f t="shared" ca="1" si="26"/>
-        <v>33861656354.709976</v>
+        <f t="shared" si="26"/>
+        <v>33711644854.151276</v>
       </c>
       <c r="H102" s="25">
-        <f t="shared" ca="1" si="26"/>
-        <v>36923184481.293411</v>
+        <f t="shared" si="26"/>
+        <v>36560867689.332146</v>
       </c>
       <c r="I102" s="25">
-        <f t="shared" ca="1" si="26"/>
-        <v>39506915844.833527</v>
+        <f t="shared" si="26"/>
+        <v>38943660980.081429</v>
       </c>
       <c r="J102" s="25">
-        <f t="shared" ca="1" si="26"/>
-        <v>41255110048.204208</v>
+        <f t="shared" si="26"/>
+        <v>40528300465.266823</v>
       </c>
       <c r="K102" s="25">
-        <f t="shared" ca="1" si="26"/>
-        <v>42601424244.322952</v>
+        <f t="shared" si="26"/>
+        <v>41722505706.841148</v>
       </c>
     </row>
     <row r="103" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6409,7 +6409,7 @@
     </row>
     <row r="104" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C104" s="13" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E104" s="18"/>
       <c r="F104" s="18"/>
@@ -6421,7 +6421,7 @@
     </row>
     <row r="105" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C105" s="17" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D105" s="10">
         <v>160000000</v>
@@ -6455,7 +6455,7 @@
     </row>
     <row r="106" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C106" s="17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="D106" s="10">
         <v>262391813</v>
@@ -6489,7 +6489,7 @@
     </row>
     <row r="107" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C107" s="17" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D107" s="10">
         <v>2133034809</v>
@@ -6523,7 +6523,7 @@
     </row>
     <row r="108" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C108" s="17" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D108" s="10">
         <v>0</v>
@@ -6557,7 +6557,7 @@
     </row>
     <row r="109" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C109" s="17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="D109" s="10">
         <v>3902562714</v>
@@ -6569,29 +6569,29 @@
         <v>6518269201</v>
       </c>
       <c r="G109" s="19">
-        <f ca="1">G247</f>
-        <v>8151808741.9975529</v>
+        <f>G247</f>
+        <v>8301820242.5562515</v>
       </c>
       <c r="H109" s="19">
-        <f ca="1">H247</f>
-        <v>10259284872.207178</v>
+        <f>H247</f>
+        <v>10612002936.809132</v>
       </c>
       <c r="I109" s="19">
-        <f ca="1">I247</f>
-        <v>12694674631.472486</v>
+        <f>I247</f>
+        <v>13237104502.76314</v>
       </c>
       <c r="J109" s="19">
-        <f ca="1">J247</f>
-        <v>15492815693.536009</v>
+        <f>J247</f>
+        <v>16189513551.154734</v>
       </c>
       <c r="K109" s="19">
-        <f ca="1">K247</f>
-        <v>18771623332.594582</v>
+        <f>K247</f>
+        <v>19613535865.477989</v>
       </c>
     </row>
     <row r="110" spans="3:11" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C110" s="104" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D110" s="56">
         <f t="shared" ref="D110:K110" si="27">SUM(D105:D109)</f>
@@ -6606,29 +6606,29 @@
         <v>9115750503</v>
       </c>
       <c r="G110" s="56">
-        <f t="shared" ca="1" si="27"/>
-        <v>10879314177.179352</v>
+        <f t="shared" si="27"/>
+        <v>11029325677.73805</v>
       </c>
       <c r="H110" s="56">
-        <f t="shared" ca="1" si="27"/>
-        <v>13131871090.798656</v>
+        <f t="shared" si="27"/>
+        <v>13484589155.400612</v>
       </c>
       <c r="I110" s="56">
-        <f t="shared" ca="1" si="27"/>
-        <v>15727183285.18198</v>
+        <f t="shared" si="27"/>
+        <v>16269613156.472633</v>
       </c>
       <c r="J110" s="56">
-        <f t="shared" ca="1" si="27"/>
-        <v>18698942948.119873</v>
+        <f t="shared" si="27"/>
+        <v>19395640805.738598</v>
       </c>
       <c r="K110" s="56">
-        <f t="shared" ca="1" si="27"/>
-        <v>22165148152.323792</v>
+        <f t="shared" si="27"/>
+        <v>23007060685.207199</v>
       </c>
     </row>
     <row r="111" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C111" s="17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D111" s="10">
         <v>126112997</v>
@@ -6640,29 +6640,29 @@
         <v>-5551093</v>
       </c>
       <c r="G111" s="19">
-        <f ca="1">G253</f>
+        <f>G253</f>
         <v>-5551093</v>
       </c>
       <c r="H111" s="19">
-        <f ca="1">H253</f>
+        <f>H253</f>
         <v>-5551093</v>
       </c>
       <c r="I111" s="19">
-        <f ca="1">I253</f>
+        <f>I253</f>
         <v>-5551093</v>
       </c>
       <c r="J111" s="19">
-        <f ca="1">J253</f>
+        <f>J253</f>
         <v>-5551093</v>
       </c>
       <c r="K111" s="19">
-        <f ca="1">K253</f>
+        <f>K253</f>
         <v>-5551093</v>
       </c>
     </row>
     <row r="112" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C112" s="26" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D112" s="12">
         <f t="shared" ref="D112:K112" si="28">SUM(D110:D111)</f>
@@ -6677,24 +6677,24 @@
         <v>9110199410</v>
       </c>
       <c r="G112" s="12">
-        <f t="shared" ca="1" si="28"/>
-        <v>10873763084.179352</v>
+        <f t="shared" si="28"/>
+        <v>11023774584.73805</v>
       </c>
       <c r="H112" s="12">
-        <f t="shared" ca="1" si="28"/>
-        <v>13126319997.798656</v>
+        <f t="shared" si="28"/>
+        <v>13479038062.400612</v>
       </c>
       <c r="I112" s="12">
-        <f t="shared" ca="1" si="28"/>
-        <v>15721632192.18198</v>
+        <f t="shared" si="28"/>
+        <v>16264062063.472633</v>
       </c>
       <c r="J112" s="12">
-        <f t="shared" ca="1" si="28"/>
-        <v>18693391855.119873</v>
+        <f t="shared" si="28"/>
+        <v>19390089712.738598</v>
       </c>
       <c r="K112" s="12">
-        <f t="shared" ca="1" si="28"/>
-        <v>22159597059.323792</v>
+        <f t="shared" si="28"/>
+        <v>23001509592.207199</v>
       </c>
     </row>
     <row r="113" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6708,7 +6708,7 @@
     </row>
     <row r="114" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C114" s="13" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D114" s="14">
         <f t="shared" ref="D114:K114" si="29">D102+D112</f>
@@ -6723,24 +6723,24 @@
         <v>41334187181</v>
       </c>
       <c r="G114" s="14">
-        <f t="shared" ca="1" si="29"/>
+        <f t="shared" si="29"/>
         <v>44735419438.889328</v>
       </c>
       <c r="H114" s="14">
-        <f t="shared" ca="1" si="29"/>
-        <v>50049504479.092072</v>
+        <f t="shared" si="29"/>
+        <v>50039905751.732758</v>
       </c>
       <c r="I114" s="14">
-        <f t="shared" ca="1" si="29"/>
-        <v>55228548037.015503</v>
+        <f t="shared" si="29"/>
+        <v>55207723043.554062</v>
       </c>
       <c r="J114" s="14">
-        <f t="shared" ca="1" si="29"/>
-        <v>59948501903.324081</v>
+        <f t="shared" si="29"/>
+        <v>59918390178.005417</v>
       </c>
       <c r="K114" s="14">
-        <f t="shared" ca="1" si="29"/>
-        <v>64761021303.646744</v>
+        <f t="shared" si="29"/>
+        <v>64724015299.048347</v>
       </c>
     </row>
     <row r="115" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6754,7 +6754,7 @@
     </row>
     <row r="116" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C116" s="6" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D116" s="109">
         <f t="shared" ref="D116:K116" si="30">D80-D114</f>
@@ -6769,30 +6769,30 @@
         <v>0</v>
       </c>
       <c r="G116" s="109">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="H116" s="109">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="I116" s="109">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="J116" s="109">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
       <c r="K116" s="59">
-        <f t="shared" ca="1" si="30"/>
+        <f t="shared" si="30"/>
         <v>0</v>
       </c>
     </row>
     <row r="117" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="118" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C118" s="38" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D118" s="96"/>
       <c r="E118" s="45"/>
@@ -6805,7 +6805,7 @@
     </row>
     <row r="119" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C119" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D119" s="40"/>
       <c r="E119" s="40"/>
@@ -6833,7 +6833,7 @@
     </row>
     <row r="120" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C120" s="42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D120" s="98"/>
       <c r="E120" s="43"/>
@@ -6862,35 +6862,35 @@
     <row r="121" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="122" spans="3:11" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C122" s="17" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D122" s="65"/>
       <c r="E122" s="65"/>
       <c r="F122" s="67"/>
       <c r="G122" s="136">
-        <f ca="1">G34</f>
-        <v>2016855214.1801429</v>
+        <f>G34</f>
+        <v>2166866714.738843</v>
       </c>
       <c r="H122" s="136">
-        <f ca="1">H34</f>
-        <v>2490498826.2428308</v>
+        <f>H34</f>
+        <v>2721694202.4606042</v>
       </c>
       <c r="I122" s="136">
-        <f ca="1">I34</f>
-        <v>2908362518.1367617</v>
+        <f>I34</f>
+        <v>3141980836.1539602</v>
       </c>
       <c r="J122" s="136">
-        <f ca="1">J34</f>
-        <v>3350470671.5003076</v>
+        <f>J34</f>
+        <v>3549105312.103096</v>
       </c>
       <c r="K122" s="136">
-        <f ca="1">K34</f>
-        <v>3915098385.4421186</v>
+        <f>K34</f>
+        <v>4098035934.9291773</v>
       </c>
     </row>
     <row r="123" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C123" s="17" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="D123" s="67"/>
       <c r="E123" s="66"/>
@@ -6918,7 +6918,7 @@
     </row>
     <row r="124" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C124" s="17" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D124" s="67"/>
       <c r="E124" s="66"/>
@@ -6946,35 +6946,35 @@
     </row>
     <row r="125" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C125" s="17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D125" s="67"/>
       <c r="E125" s="66"/>
       <c r="F125" s="66"/>
       <c r="G125" s="137">
-        <f ca="1">G87-F87</f>
-        <v>-78549258.563609004</v>
+        <f>G87-F87</f>
+        <v>-19892773.050287247</v>
       </c>
       <c r="H125" s="137">
-        <f ca="1">H87-G87</f>
-        <v>185200931.70164025</v>
+        <f>H87-G87</f>
+        <v>216944903.38898647</v>
       </c>
       <c r="I125" s="137">
-        <f ca="1">I87-H87</f>
-        <v>163390243.40689397</v>
+        <f>I87-H87</f>
+        <v>164337645.77290142</v>
       </c>
       <c r="J125" s="137">
-        <f ca="1">J87-I87</f>
-        <v>172870149.26527405</v>
+        <f>J87-I87</f>
+        <v>159191067.59607792</v>
       </c>
       <c r="K125" s="137">
-        <f ca="1">K87-J87</f>
-        <v>220776921.76866198</v>
+        <f>K87-J87</f>
+        <v>214639151.03640532</v>
       </c>
     </row>
     <row r="126" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C126" s="17" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D126" s="66"/>
       <c r="E126" s="66"/>
@@ -7002,30 +7002,30 @@
     </row>
     <row r="127" spans="3:11" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C127" s="13" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D127" s="65"/>
       <c r="E127" s="65"/>
       <c r="F127" s="65"/>
       <c r="G127" s="138">
-        <f ca="1">SUM(G122:G126)</f>
-        <v>-729930712.11745024</v>
+        <f>SUM(G122:G126)</f>
+        <v>-521262726.04542828</v>
       </c>
       <c r="H127" s="138">
-        <f ca="1">SUM(H122:H126)</f>
-        <v>12669205.731692314</v>
+        <f>SUM(H122:H126)</f>
+        <v>275608553.63681221</v>
       </c>
       <c r="I127" s="138">
-        <f ca="1">SUM(I122:I126)</f>
-        <v>668451450.14309883</v>
+        <f>SUM(I122:I126)</f>
+        <v>903017170.5263052</v>
       </c>
       <c r="J127" s="138">
-        <f ca="1">SUM(J122:J126)</f>
-        <v>1574027916.3458567</v>
+        <f>SUM(J122:J126)</f>
+        <v>1758983475.2794485</v>
       </c>
       <c r="K127" s="138">
-        <f ca="1">SUM(K122:K126)</f>
-        <v>2260203842.198061</v>
+        <f>SUM(K122:K126)</f>
+        <v>2437003620.9528627</v>
       </c>
     </row>
     <row r="128" spans="3:11" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7040,7 +7040,7 @@
     </row>
     <row r="129" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C129" s="63" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D129" s="66"/>
       <c r="E129" s="66"/>
@@ -7053,7 +7053,7 @@
     </row>
     <row r="130" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C130" s="17" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="D130" s="66"/>
       <c r="E130" s="66"/>
@@ -7081,30 +7081,30 @@
     </row>
     <row r="131" spans="3:11" s="13" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C131" s="13" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D131" s="65"/>
       <c r="E131" s="65"/>
       <c r="F131" s="65"/>
       <c r="G131" s="138">
-        <f ca="1">G127+G130</f>
-        <v>-1677563293.5874677</v>
+        <f>G127+G130</f>
+        <v>-1468895307.5154457</v>
       </c>
       <c r="H131" s="138">
-        <f ca="1">H127+H130</f>
-        <v>-891083972.91663361</v>
+        <f>H127+H130</f>
+        <v>-628144625.01151371</v>
       </c>
       <c r="I131" s="138">
-        <f ca="1">I127+I130</f>
-        <v>-175516507.55458069</v>
+        <f>I127+I130</f>
+        <v>59049212.828625679</v>
       </c>
       <c r="J131" s="138">
-        <f ca="1">J127+J130</f>
-        <v>831737841.08416653</v>
+        <f>J127+J130</f>
+        <v>1016693400.0177584</v>
       </c>
       <c r="K131" s="138">
-        <f ca="1">K127+K130</f>
-        <v>1460200221.1968632</v>
+        <f>K127+K130</f>
+        <v>1636999999.9516649</v>
       </c>
     </row>
     <row r="132" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7119,7 +7119,7 @@
     </row>
     <row r="133" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C133" s="82" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D133" s="99"/>
       <c r="E133" s="83"/>
@@ -7132,7 +7132,7 @@
     </row>
     <row r="134" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C134" s="17" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D134" s="67"/>
       <c r="E134" s="66"/>
@@ -7160,7 +7160,7 @@
     </row>
     <row r="135" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C135" s="17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D135" s="67"/>
       <c r="E135" s="66"/>
@@ -7188,7 +7188,7 @@
     </row>
     <row r="136" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C136" s="13" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="D136" s="67"/>
       <c r="E136" s="69"/>
@@ -7226,7 +7226,7 @@
     </row>
     <row r="138" spans="3:11" s="35" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C138" s="44" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="D138" s="100"/>
       <c r="E138" s="72"/>
@@ -7239,7 +7239,7 @@
     </row>
     <row r="139" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C139" s="17" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="D139" s="67"/>
       <c r="E139" s="66"/>
@@ -7249,25 +7249,25 @@
         <v>-383315673.18259084</v>
       </c>
       <c r="H139" s="137">
-        <f ca="1">H246</f>
-        <v>-383022696.03320432</v>
+        <f>H246</f>
+        <v>-411511508.20772451</v>
       </c>
       <c r="I139" s="137">
-        <f ca="1">I246</f>
-        <v>-472972758.87145418</v>
+        <f>I246</f>
+        <v>-516879270.19995314</v>
       </c>
       <c r="J139" s="137">
-        <f ca="1">J246</f>
-        <v>-552329609.43678486</v>
+        <f>J246</f>
+        <v>-596696263.71150148</v>
       </c>
       <c r="K139" s="137">
-        <f ca="1">K246</f>
-        <v>-636290746.38354528</v>
+        <f>K246</f>
+        <v>-674013620.60592425</v>
       </c>
     </row>
     <row r="140" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C140" s="17" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="D140" s="67"/>
       <c r="E140" s="66"/>
@@ -7295,58 +7295,58 @@
     </row>
     <row r="141" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C141" s="17" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="D141" s="67"/>
       <c r="E141" s="66"/>
       <c r="F141" s="66"/>
       <c r="G141" s="137">
-        <f ca="1">G314+G310</f>
-        <v>1530200932.2272496</v>
+        <f>G314+G310</f>
+        <v>1321532946.1552277</v>
       </c>
       <c r="H141" s="137">
-        <f ca="1">H314+H310</f>
-        <v>2522862653.005434</v>
+        <f>H314+H310</f>
+        <v>2278813389.9155216</v>
       </c>
       <c r="I141" s="137">
-        <f ca="1">I314+I310</f>
-        <v>2062282562.0086641</v>
+        <f>I314+I310</f>
+        <v>1860397086.8518205</v>
       </c>
       <c r="J141" s="137">
-        <f ca="1">J314+J310</f>
-        <v>1228857652.5553963</v>
+        <f>J314+J310</f>
+        <v>1078982016.0393066</v>
       </c>
       <c r="K141" s="137">
-        <f ca="1">K314+K310</f>
-        <v>764411662.85628676</v>
+        <f>K314+K310</f>
+        <v>618440479.04412365</v>
       </c>
     </row>
     <row r="142" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C142" s="13" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="D142" s="65"/>
       <c r="E142" s="69"/>
       <c r="F142" s="69"/>
       <c r="G142" s="140">
-        <f ca="1">SUM(G139:G141)+G396</f>
-        <v>870322247.30437934</v>
+        <f>SUM(G139:G141)+G396</f>
+        <v>661654261.23235738</v>
       </c>
       <c r="H142" s="140">
-        <f ca="1">SUM(H139:H141)+H396</f>
-        <v>1837297119.8573258</v>
+        <f>SUM(H139:H141)+H396</f>
+        <v>1564759044.5928931</v>
       </c>
       <c r="I142" s="140">
-        <f ca="1">SUM(I139:I141)+I396</f>
-        <v>1256988200.2916033</v>
+        <f>SUM(I139:I141)+I396</f>
+        <v>1011196213.8062608</v>
       </c>
       <c r="J142" s="140">
-        <f ca="1">SUM(J139:J141)+J396</f>
-        <v>311228202.69058108</v>
+        <f>SUM(J139:J141)+J396</f>
+        <v>116985911.89977479</v>
       </c>
       <c r="K142" s="140">
-        <f ca="1">SUM(K139:K141)+K396</f>
-        <v>-272390849.82862949</v>
+        <f>SUM(K139:K141)+K396</f>
+        <v>-456084907.86317158</v>
       </c>
     </row>
     <row r="143" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7362,35 +7362,35 @@
     </row>
     <row r="144" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C144" s="13" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="D144" s="65"/>
       <c r="E144" s="69"/>
       <c r="F144" s="69"/>
       <c r="G144" s="140">
-        <f ca="1">G131+G136+G142</f>
+        <f>G131+G136+G142</f>
         <v>-1592170940.296</v>
       </c>
       <c r="H144" s="140">
-        <f ca="1">H131+H136+H142</f>
-        <v>70389242.882453203</v>
+        <f>H131+H136+H142</f>
+        <v>60790515.52314043</v>
       </c>
       <c r="I144" s="140">
-        <f ca="1">I131+I136+I142</f>
-        <v>116051682.03824997</v>
+        <f>I131+I136+I142</f>
+        <v>104825415.93611383</v>
       </c>
       <c r="J144" s="140">
-        <f ca="1">J131+J136+J142</f>
-        <v>94864997.852398396</v>
+        <f>J131+J136+J142</f>
+        <v>85578265.995183945</v>
       </c>
       <c r="K144" s="140">
-        <f ca="1">K131+K136+K142</f>
-        <v>56527452.017547846</v>
+        <f>K131+K136+K142</f>
+        <v>49633172.737807512</v>
       </c>
     </row>
     <row r="145" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C145" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="D145" s="65"/>
       <c r="E145" s="69"/>
@@ -7400,48 +7400,48 @@
         <v>3458917393</v>
       </c>
       <c r="H145" s="140">
-        <f ca="1">G66</f>
+        <f>G66</f>
         <v>1866746452.704</v>
       </c>
       <c r="I145" s="140">
-        <f ca="1">H66</f>
-        <v>1937135695.5864532</v>
+        <f>H66</f>
+        <v>1927536968.2271404</v>
       </c>
       <c r="J145" s="140">
-        <f ca="1">I66</f>
-        <v>2053187377.6247032</v>
+        <f>I66</f>
+        <v>2032362384.1632543</v>
       </c>
       <c r="K145" s="140">
-        <f ca="1">J66</f>
-        <v>2148052375.4771013</v>
+        <f>J66</f>
+        <v>2117940650.1584382</v>
       </c>
     </row>
     <row r="146" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C146" s="13" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="D146" s="67"/>
       <c r="E146" s="69"/>
       <c r="F146" s="69"/>
       <c r="G146" s="140">
-        <f ca="1">SUM(G144:G145)</f>
+        <f>SUM(G144:G145)</f>
         <v>1866746452.704</v>
       </c>
       <c r="H146" s="140">
-        <f ca="1">SUM(H144:H145)</f>
-        <v>1937135695.5864532</v>
+        <f>SUM(H144:H145)</f>
+        <v>1927536968.2271404</v>
       </c>
       <c r="I146" s="140">
-        <f ca="1">SUM(I144:I145)</f>
-        <v>2053187377.6247032</v>
+        <f>SUM(I144:I145)</f>
+        <v>2032362384.1632543</v>
       </c>
       <c r="J146" s="140">
-        <f ca="1">SUM(J144:J145)</f>
-        <v>2148052375.4771013</v>
+        <f>SUM(J144:J145)</f>
+        <v>2117940650.1584382</v>
       </c>
       <c r="K146" s="140">
-        <f ca="1">SUM(K144:K145)</f>
-        <v>2204579827.4946489</v>
+        <f>SUM(K144:K145)</f>
+        <v>2167573822.896246</v>
       </c>
     </row>
     <row r="147" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -7457,36 +7457,36 @@
     </row>
     <row r="148" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C148" s="13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D148" s="89"/>
       <c r="E148" s="89"/>
       <c r="F148" s="66"/>
       <c r="G148" s="59">
-        <f ca="1">G146-G66</f>
+        <f>G146-G66</f>
         <v>0</v>
       </c>
       <c r="H148" s="59">
-        <f ca="1">H146-H66</f>
+        <f>H146-H66</f>
         <v>0</v>
       </c>
       <c r="I148" s="59">
-        <f ca="1">I146-I66</f>
+        <f>I146-I66</f>
         <v>0</v>
       </c>
       <c r="J148" s="59">
-        <f ca="1">J146-J66</f>
+        <f>J146-J66</f>
         <v>0</v>
       </c>
       <c r="K148" s="59">
-        <f ca="1">K146-K66</f>
+        <f>K146-K66</f>
         <v>0</v>
       </c>
     </row>
     <row r="149" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="150" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C150" s="38" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="D150" s="95"/>
       <c r="E150" s="39"/>
@@ -7499,7 +7499,7 @@
     </row>
     <row r="151" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C151" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D151" s="40">
         <f t="shared" ref="D151:K151" si="31">D$13</f>
@@ -7536,7 +7536,7 @@
     </row>
     <row r="152" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C152" s="42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D152" s="86">
         <f t="shared" ref="D152:K152" si="32">D$14</f>
@@ -7574,7 +7574,7 @@
     <row r="153" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="154" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C154" s="17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D154" s="130"/>
       <c r="E154" s="60">
@@ -7608,7 +7608,7 @@
     </row>
     <row r="155" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C155" s="29" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="D155" s="64">
         <v>361131630</v>
@@ -7644,7 +7644,7 @@
     </row>
     <row r="156" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C156" s="29" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D156" s="64">
         <v>75771163</v>
@@ -7678,7 +7678,7 @@
     </row>
     <row r="157" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C157" s="16" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D157" s="87">
         <f>D70</f>
@@ -7726,7 +7726,7 @@
     </row>
     <row r="159" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C159" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="D159" s="22">
         <f>D155/D18</f>
@@ -7763,7 +7763,7 @@
     </row>
     <row r="160" spans="3:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C160" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="D160" s="22"/>
       <c r="E160" s="22">
@@ -7806,7 +7806,7 @@
     </row>
     <row r="162" spans="1:11" s="35" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C162" s="44" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="D162" s="46"/>
       <c r="E162" s="46"/>
@@ -7830,7 +7830,7 @@
     </row>
     <row r="164" spans="1:11" s="31" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C164" s="35" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="D164" s="171">
         <f t="shared" ref="D164:K164" si="35">ABS(D279+D291)</f>
@@ -7869,7 +7869,7 @@
       <c r="A165" s="32"/>
       <c r="B165" s="32"/>
       <c r="C165" s="24" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="D165" s="36">
         <f t="shared" ref="D165:K165" si="36">D164/D18</f>
@@ -7906,7 +7906,7 @@
     </row>
     <row r="166" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="C166" s="37" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="D166" s="30">
         <f t="shared" ref="D166:K166" si="37">D156+D164</f>
@@ -7943,7 +7943,7 @@
     </row>
     <row r="168" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C168" s="13" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D168" s="102"/>
       <c r="E168" s="13"/>
@@ -7956,7 +7956,7 @@
     </row>
     <row r="169" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C169" s="47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D169" s="48">
         <f t="shared" ref="D169:K169" si="38">D$13</f>
@@ -7993,7 +7993,7 @@
     </row>
     <row r="170" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C170" s="42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D170" s="43">
         <f t="shared" ref="D170:K170" si="39">D$14</f>
@@ -8038,7 +8038,7 @@
     </row>
     <row r="172" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C172" s="17" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="D172" s="160">
         <v>5297068637</v>
@@ -8072,7 +8072,7 @@
     </row>
     <row r="173" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C173" s="17" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D173" s="160">
         <v>2086063819</v>
@@ -8106,7 +8106,7 @@
     </row>
     <row r="174" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C174" s="17" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="D174" s="160">
         <v>223764567</v>
@@ -8140,13 +8140,13 @@
     </row>
     <row r="175" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C175" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="D175" s="160" t="s">
         <v>182</v>
       </c>
-      <c r="D175" s="160" t="s">
-        <v>183</v>
-      </c>
       <c r="E175" s="160" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F175" s="160">
         <v>29216196</v>
@@ -8174,7 +8174,7 @@
     </row>
     <row r="176" spans="1:11" x14ac:dyDescent="0.25">
       <c r="C176" s="17" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D176" s="160">
         <v>1805005316</v>
@@ -8208,7 +8208,7 @@
     </row>
     <row r="177" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C177" s="17" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="D177" s="160">
         <v>212172</v>
@@ -8242,7 +8242,7 @@
     </row>
     <row r="178" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C178" s="37" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D178" s="162">
         <f t="shared" ref="D178:K178" si="41">SUM(D172:D177)</f>
@@ -8290,7 +8290,7 @@
     </row>
     <row r="180" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C180" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D180" s="66">
         <f t="shared" ref="D180:K180" si="42">D178-D18</f>
@@ -8538,7 +8538,7 @@
     </row>
     <row r="189" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C189" s="13" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D189" s="102"/>
       <c r="E189" s="13"/>
@@ -8551,7 +8551,7 @@
     </row>
     <row r="190" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C190" s="47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D190" s="48">
         <f t="shared" ref="D190:K190" si="46">D$13</f>
@@ -8588,7 +8588,7 @@
     </row>
     <row r="191" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C191" s="42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D191" s="43">
         <f t="shared" ref="D191:K191" si="47">D$14</f>
@@ -8633,7 +8633,7 @@
     </row>
     <row r="193" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C193" s="84" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D193" s="160">
         <v>2239890778</v>
@@ -8645,29 +8645,29 @@
         <v>6963884903</v>
       </c>
       <c r="G193" s="161">
-        <f ca="1">G318</f>
-        <v>6756494037.6363268</v>
+        <f>G318</f>
+        <v>6568239919.2325459</v>
       </c>
       <c r="H193" s="161">
-        <f ca="1">H318</f>
-        <v>7218772371.2625799</v>
+        <f>H318</f>
+        <v>6858864679.4139566</v>
       </c>
       <c r="I193" s="161">
-        <f ca="1">I318</f>
-        <v>7780036844.0131531</v>
+        <f>I318</f>
+        <v>7416760639.4370899</v>
       </c>
       <c r="J193" s="161">
-        <f ca="1">J318</f>
-        <v>8182903054.4936485</v>
+        <f>J318</f>
+        <v>7872220495.6001749</v>
       </c>
       <c r="K193" s="161">
-        <f ca="1">K318</f>
-        <v>8426897780.7023354</v>
+        <f>K318</f>
+        <v>8136375388.8221512</v>
       </c>
     </row>
     <row r="194" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C194" s="84" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D194" s="160">
         <v>1812939327</v>
@@ -8701,7 +8701,7 @@
     </row>
     <row r="195" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C195" s="37" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D195" s="162">
         <f t="shared" ref="D195:K195" si="48">SUM(D193:D194)</f>
@@ -8716,24 +8716,24 @@
         <v>8941506786</v>
       </c>
       <c r="G195" s="162">
-        <f t="shared" ca="1" si="48"/>
-        <v>8832997014.7863274</v>
+        <f t="shared" si="48"/>
+        <v>8644742896.3825455</v>
       </c>
       <c r="H195" s="162">
-        <f t="shared" ca="1" si="48"/>
-        <v>9399100497.2700806</v>
+        <f t="shared" si="48"/>
+        <v>9039192805.4214573</v>
       </c>
       <c r="I195" s="162">
-        <f t="shared" ca="1" si="48"/>
-        <v>10069381376.321028</v>
+        <f t="shared" si="48"/>
+        <v>9706105171.7449646</v>
       </c>
       <c r="J195" s="162">
-        <f t="shared" ca="1" si="48"/>
-        <v>10586714813.416918</v>
+        <f t="shared" si="48"/>
+        <v>10276032254.523443</v>
       </c>
       <c r="K195" s="162">
-        <f t="shared" ca="1" si="48"/>
-        <v>10950900127.571768</v>
+        <f t="shared" si="48"/>
+        <v>10660377735.691584</v>
       </c>
     </row>
     <row r="196" spans="3:11" x14ac:dyDescent="0.25">
@@ -8749,7 +8749,7 @@
     </row>
     <row r="197" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C197" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="D197" s="66">
         <f t="shared" ref="D197:K197" si="49">D195-ABS(D21)</f>
@@ -8764,23 +8764,23 @@
         <v>0</v>
       </c>
       <c r="G197" s="66">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="H197" s="66">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="I197" s="66">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="J197" s="66">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="K197" s="66">
-        <f t="shared" ca="1" si="49"/>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
     </row>
@@ -8796,7 +8796,7 @@
     </row>
     <row r="199" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C199" s="159" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="D199" s="1">
         <f t="shared" ref="D199:K199" si="50">D193/D172</f>
@@ -8811,29 +8811,29 @@
         <v>0.70393414461570136</v>
       </c>
       <c r="G199" s="1">
-        <f t="shared" ca="1" si="50"/>
-        <v>0.75344962388894998</v>
+        <f t="shared" si="50"/>
+        <v>0.73245648840821542</v>
       </c>
       <c r="H199" s="1">
-        <f t="shared" ca="1" si="50"/>
-        <v>0.71476413919916126</v>
+        <f t="shared" si="50"/>
+        <v>0.67912800907550908</v>
       </c>
       <c r="I199" s="1">
-        <f t="shared" ca="1" si="50"/>
-        <v>0.69076448563951087</v>
+        <f t="shared" si="50"/>
+        <v>0.65851035810383496</v>
       </c>
       <c r="J199" s="1">
-        <f t="shared" ca="1" si="50"/>
-        <v>0.66249084125306013</v>
+        <f t="shared" si="50"/>
+        <v>0.6373378670050075</v>
       </c>
       <c r="K199" s="1">
-        <f t="shared" ca="1" si="50"/>
-        <v>0.62896014781518428</v>
+        <f t="shared" si="50"/>
+        <v>0.60727636674938945</v>
       </c>
     </row>
     <row r="200" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C200" s="159" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D200" s="1">
         <f>D194/D173</f>
@@ -8881,12 +8881,12 @@
     </row>
     <row r="202" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C202" s="13" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
     </row>
     <row r="203" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C203" s="47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D203" s="48">
         <f t="shared" ref="D203:K203" si="51">D$13</f>
@@ -8923,7 +8923,7 @@
     </row>
     <row r="204" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C204" s="42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D204" s="86">
         <f t="shared" ref="D204:K204" si="52">D$14</f>
@@ -8963,13 +8963,13 @@
     </row>
     <row r="206" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C206" s="13" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D206" s="6"/>
     </row>
     <row r="207" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C207" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="D207" s="27">
         <f t="shared" ref="D207:F209" si="53">D61</f>
@@ -9006,7 +9006,7 @@
     </row>
     <row r="208" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C208" s="17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D208" s="27">
         <f t="shared" si="53"/>
@@ -9043,7 +9043,7 @@
     </row>
     <row r="209" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C209" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D209" s="27">
         <f t="shared" si="53"/>
@@ -9080,7 +9080,7 @@
     </row>
     <row r="210" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C210" s="13" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D210" s="78">
         <f t="shared" ref="D210:K210" si="54">SUM(D207:D209)</f>
@@ -9127,7 +9127,7 @@
     </row>
     <row r="212" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C212" s="13" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="E212" s="28"/>
       <c r="F212" s="28"/>
@@ -9139,7 +9139,7 @@
     </row>
     <row r="213" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C213" s="17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D213" s="19">
         <f t="shared" ref="D213:F214" si="55">D88</f>
@@ -9176,7 +9176,7 @@
     </row>
     <row r="214" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C214" s="17" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="D214" s="19">
         <f t="shared" si="55"/>
@@ -9213,7 +9213,7 @@
     </row>
     <row r="215" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C215" s="13" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D215" s="79">
         <f t="shared" ref="D215:K215" si="56">SUM(D213:D214)</f>
@@ -9259,7 +9259,7 @@
     </row>
     <row r="217" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C217" s="6" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D217" s="19">
         <f t="shared" ref="D217:K217" si="57">D210-D215</f>
@@ -9296,7 +9296,7 @@
     </row>
     <row r="218" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C218" s="6" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D218" s="22">
         <f t="shared" ref="D218:K218" si="58">D217/D18</f>
@@ -9333,7 +9333,7 @@
     </row>
     <row r="219" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C219" s="6" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="D219" s="19"/>
       <c r="E219" s="59">
@@ -9377,7 +9377,7 @@
     </row>
     <row r="221" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C221" s="13" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="G221" s="106"/>
       <c r="H221" s="106"/>
@@ -9387,7 +9387,7 @@
     </row>
     <row r="222" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C222" s="17" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D222" s="91">
         <f>D209/-D20*365</f>
@@ -9424,7 +9424,7 @@
     </row>
     <row r="223" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C223" s="17" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D223" s="91">
         <f t="shared" ref="D223:K223" si="60">D208/D18*365</f>
@@ -9461,7 +9461,7 @@
     </row>
     <row r="224" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C224" s="17" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="D224" s="91">
         <f t="shared" ref="D224:K224" si="61">D213/-D20*365</f>
@@ -9509,12 +9509,12 @@
     </row>
     <row r="226" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C226" s="13" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="227" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C227" s="47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D227" s="48">
         <f t="shared" ref="D227:K227" si="62">D$13</f>
@@ -9551,7 +9551,7 @@
     </row>
     <row r="228" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C228" s="42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D228" s="86">
         <f t="shared" ref="D228:K228" si="63">D$14</f>
@@ -9588,13 +9588,13 @@
     </row>
     <row r="230" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C230" s="13" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="D230" s="7"/>
     </row>
     <row r="231" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C231" s="17" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="D231" s="59">
         <f>D66+D64</f>
@@ -9609,29 +9609,29 @@
         <v>10499227965</v>
       </c>
       <c r="G231" s="59">
-        <f t="shared" ca="1" si="64"/>
+        <f t="shared" si="64"/>
         <v>9963103610.5039997</v>
       </c>
       <c r="H231" s="59">
-        <f t="shared" ca="1" si="64"/>
-        <v>11005055712.322453</v>
+        <f t="shared" si="64"/>
+        <v>10995456984.96314</v>
       </c>
       <c r="I231" s="59">
-        <f t="shared" ca="1" si="64"/>
-        <v>12027899396.034304</v>
+        <f t="shared" si="64"/>
+        <v>12007074402.572855</v>
       </c>
       <c r="J231" s="59">
-        <f t="shared" ca="1" si="64"/>
-        <v>12920741355.359474</v>
+        <f t="shared" si="64"/>
+        <v>12890629630.04081</v>
       </c>
       <c r="K231" s="59">
-        <f t="shared" ca="1" si="64"/>
-        <v>13839083925.767612</v>
+        <f t="shared" si="64"/>
+        <v>13802077921.169209</v>
       </c>
     </row>
     <row r="232" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C232" s="17" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="D232" s="59"/>
       <c r="E232" s="59">
@@ -9643,29 +9643,29 @@
         <v>6943216417.5</v>
       </c>
       <c r="G232" s="59">
-        <f ca="1">IF($D$301=1,IFERROR(AVERAGE(F231,G231),F231),F231)</f>
-        <v>10231165787.751999</v>
+        <f>IF($D$301=1,IFERROR(AVERAGE(F231,G231),F231),F231)</f>
+        <v>10499227965</v>
       </c>
       <c r="H232" s="59">
-        <f ca="1">IF($D$301=1,IFERROR(AVERAGE(G231,H231),G231),G231)</f>
-        <v>10484079661.413227</v>
+        <f>IF($D$301=1,IFERROR(AVERAGE(G231,H231),G231),G231)</f>
+        <v>9963103610.5039997</v>
       </c>
       <c r="I232" s="59">
-        <f ca="1">IF($D$301=1,IFERROR(AVERAGE(H231,I231),H231),H231)</f>
-        <v>11516477554.178379</v>
+        <f>IF($D$301=1,IFERROR(AVERAGE(H231,I231),H231),H231)</f>
+        <v>10995456984.96314</v>
       </c>
       <c r="J232" s="59">
-        <f ca="1">IF($D$301=1,IFERROR(AVERAGE(I231,J231),I231),I231)</f>
-        <v>12474320375.696888</v>
+        <f>IF($D$301=1,IFERROR(AVERAGE(I231,J231),I231),I231)</f>
+        <v>12007074402.572855</v>
       </c>
       <c r="K232" s="59">
-        <f ca="1">IF($D$301=1,IFERROR(AVERAGE(J231,K231),J231),J231)</f>
-        <v>13379912640.563543</v>
+        <f>IF($D$301=1,IFERROR(AVERAGE(J231,K231),J231),J231)</f>
+        <v>12890629630.04081</v>
       </c>
     </row>
     <row r="233" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C233" s="17" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="D233" s="1"/>
       <c r="E233" s="1">
@@ -9699,7 +9699,7 @@
     </row>
     <row r="234" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C234" s="6" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D234" s="101"/>
       <c r="E234" s="272">
@@ -9714,7 +9714,7 @@
     </row>
     <row r="235" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C235" s="6" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D235" s="132">
         <f>D28</f>
@@ -9751,7 +9751,7 @@
     </row>
     <row r="236" spans="3:11" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C236" s="35" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D236" s="132">
         <f>D27</f>
@@ -9766,29 +9766,29 @@
         <v>655970125</v>
       </c>
       <c r="G236" s="19">
-        <f ca="1">G233*G232</f>
-        <v>766975786.49670184</v>
+        <f>G233*G232</f>
+        <v>787070974.42444801</v>
       </c>
       <c r="H236" s="19">
-        <f ca="1">H233*H232</f>
-        <v>780868468.42743003</v>
+        <f>H233*H232</f>
+        <v>742065465.77015889</v>
       </c>
       <c r="I236" s="19">
-        <f ca="1">I233*I232</f>
-        <v>857762863.29723787</v>
+        <f>I233*I232</f>
+        <v>818956544.85617316</v>
       </c>
       <c r="J236" s="19">
-        <f ca="1">J233*J232</f>
-        <v>929104295.37221551</v>
+        <f>J233*J232</f>
+        <v>894303181.76039219</v>
       </c>
       <c r="K236" s="19">
-        <f ca="1">K233*K232</f>
-        <v>996554035.14182258</v>
+        <f>K233*K232</f>
+        <v>960111573.10477364</v>
       </c>
     </row>
     <row r="237" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C237" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="D237" s="59">
         <f t="shared" ref="D237:K237" si="65">SUM(D235:D236)</f>
@@ -9803,34 +9803,34 @@
         <v>508432272</v>
       </c>
       <c r="G237" s="59">
-        <f t="shared" ca="1" si="65"/>
-        <v>622427255.93919015</v>
+        <f t="shared" si="65"/>
+        <v>642522443.86693633</v>
       </c>
       <c r="H237" s="59">
-        <f t="shared" ca="1" si="65"/>
-        <v>622741312.30313659</v>
+        <f t="shared" si="65"/>
+        <v>583938309.64586544</v>
       </c>
       <c r="I237" s="59">
-        <f t="shared" ca="1" si="65"/>
-        <v>684071525.97205484</v>
+        <f t="shared" si="65"/>
+        <v>645265207.53099012</v>
       </c>
       <c r="J237" s="59">
-        <f t="shared" ca="1" si="65"/>
-        <v>738176539.65210795</v>
+        <f t="shared" si="65"/>
+        <v>703375426.04028463</v>
       </c>
       <c r="K237" s="59">
-        <f t="shared" ca="1" si="65"/>
-        <v>787222400.64174545</v>
+        <f t="shared" si="65"/>
+        <v>750779938.60469651</v>
       </c>
     </row>
     <row r="239" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C239" s="13" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="240" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C240" s="47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D240" s="48">
         <f t="shared" ref="D240:K240" si="66">D$13</f>
@@ -9867,7 +9867,7 @@
     </row>
     <row r="241" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C241" s="42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D241" s="86">
         <f t="shared" ref="D241:K241" si="67">D$14</f>
@@ -9904,12 +9904,12 @@
     </row>
     <row r="243" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C243" s="13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="244" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C244" s="17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D244" s="19"/>
       <c r="E244" s="59">
@@ -9925,25 +9925,25 @@
         <v>6518269201</v>
       </c>
       <c r="H244" s="59">
-        <f t="shared" ca="1" si="68"/>
-        <v>8151808741.9975529</v>
+        <f t="shared" si="68"/>
+        <v>8301820242.5562515</v>
       </c>
       <c r="I244" s="59">
-        <f t="shared" ca="1" si="68"/>
-        <v>10259284872.207178</v>
+        <f t="shared" si="68"/>
+        <v>10612002936.809132</v>
       </c>
       <c r="J244" s="59">
-        <f t="shared" ca="1" si="68"/>
-        <v>12694674631.472486</v>
+        <f t="shared" si="68"/>
+        <v>13237104502.76314</v>
       </c>
       <c r="K244" s="59">
-        <f t="shared" ca="1" si="68"/>
-        <v>15492815693.536009</v>
+        <f t="shared" si="68"/>
+        <v>16189513551.154734</v>
       </c>
     </row>
     <row r="245" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C245" s="17" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="D245" s="110">
         <f t="shared" ref="D245:K245" si="69">D35</f>
@@ -9958,29 +9958,29 @@
         <v>2018397923</v>
       </c>
       <c r="G245" s="110">
-        <f t="shared" ca="1" si="69"/>
-        <v>2016855214.1801429</v>
+        <f t="shared" si="69"/>
+        <v>2166866714.738843</v>
       </c>
       <c r="H245" s="110">
-        <f t="shared" ca="1" si="69"/>
-        <v>2490498826.2428308</v>
+        <f t="shared" si="69"/>
+        <v>2721694202.4606042</v>
       </c>
       <c r="I245" s="110">
-        <f t="shared" ca="1" si="69"/>
-        <v>2908362518.1367617</v>
+        <f t="shared" si="69"/>
+        <v>3141980836.1539602</v>
       </c>
       <c r="J245" s="110">
-        <f t="shared" ca="1" si="69"/>
-        <v>3350470671.5003076</v>
+        <f t="shared" si="69"/>
+        <v>3549105312.103096</v>
       </c>
       <c r="K245" s="110">
-        <f t="shared" ca="1" si="69"/>
-        <v>3915098385.4421186</v>
+        <f t="shared" si="69"/>
+        <v>4098035934.9291773</v>
       </c>
     </row>
     <row r="246" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C246" s="17" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="D246" s="90">
         <v>-444533688</v>
@@ -9996,25 +9996,25 @@
         <v>-383315673.18259084</v>
       </c>
       <c r="H246" s="59">
-        <f ca="1">-H255*G245</f>
-        <v>-383022696.03320432</v>
+        <f>-H255*G245</f>
+        <v>-411511508.20772451</v>
       </c>
       <c r="I246" s="59">
-        <f ca="1">-I255*H245</f>
-        <v>-472972758.87145418</v>
+        <f>-I255*H245</f>
+        <v>-516879270.19995314</v>
       </c>
       <c r="J246" s="59">
-        <f ca="1">-J255*I245</f>
-        <v>-552329609.43678486</v>
+        <f>-J255*I245</f>
+        <v>-596696263.71150148</v>
       </c>
       <c r="K246" s="59">
-        <f ca="1">-K255*J245</f>
-        <v>-636290746.38354528</v>
+        <f>-K255*J245</f>
+        <v>-674013620.60592425</v>
       </c>
     </row>
     <row r="247" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C247" s="17" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D247" s="19">
         <f>D109</f>
@@ -10029,24 +10029,24 @@
         <v>6518269201</v>
       </c>
       <c r="G247" s="19">
-        <f ca="1">SUM(G244:G246)</f>
-        <v>8151808741.9975529</v>
+        <f>SUM(G244:G246)</f>
+        <v>8301820242.5562515</v>
       </c>
       <c r="H247" s="19">
-        <f ca="1">SUM(H244:H246)</f>
-        <v>10259284872.207178</v>
+        <f>SUM(H244:H246)</f>
+        <v>10612002936.809132</v>
       </c>
       <c r="I247" s="19">
-        <f ca="1">SUM(I244:I246)</f>
-        <v>12694674631.472486</v>
+        <f>SUM(I244:I246)</f>
+        <v>13237104502.76314</v>
       </c>
       <c r="J247" s="19">
-        <f ca="1">SUM(J244:J246)</f>
-        <v>15492815693.536009</v>
+        <f>SUM(J244:J246)</f>
+        <v>16189513551.154734</v>
       </c>
       <c r="K247" s="19">
-        <f ca="1">SUM(K244:K246)</f>
-        <v>18771623332.594582</v>
+        <f>SUM(K244:K246)</f>
+        <v>19613535865.477989</v>
       </c>
     </row>
     <row r="248" spans="3:11" x14ac:dyDescent="0.25">
@@ -10062,7 +10062,7 @@
     </row>
     <row r="249" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C249" s="13" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D249" s="59"/>
       <c r="E249" s="59"/>
@@ -10075,7 +10075,7 @@
     </row>
     <row r="250" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C250" s="17" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D250" s="59"/>
       <c r="E250" s="59">
@@ -10091,25 +10091,25 @@
         <v>-5551093</v>
       </c>
       <c r="H250" s="59">
-        <f t="shared" ca="1" si="70"/>
+        <f t="shared" si="70"/>
         <v>-5551093</v>
       </c>
       <c r="I250" s="59">
-        <f t="shared" ca="1" si="70"/>
+        <f t="shared" si="70"/>
         <v>-5551093</v>
       </c>
       <c r="J250" s="59">
-        <f t="shared" ca="1" si="70"/>
+        <f t="shared" si="70"/>
         <v>-5551093</v>
       </c>
       <c r="K250" s="59">
-        <f t="shared" ca="1" si="70"/>
+        <f t="shared" si="70"/>
         <v>-5551093</v>
       </c>
     </row>
     <row r="251" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C251" s="17" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D251" s="59">
         <f>D36</f>
@@ -10124,29 +10124,29 @@
         <v>-39999184</v>
       </c>
       <c r="G251" s="59">
-        <f ca="1">G256*G34</f>
+        <f>G256*G34</f>
         <v>0</v>
       </c>
       <c r="H251" s="59">
-        <f ca="1">H256*H34</f>
+        <f>H256*H34</f>
         <v>0</v>
       </c>
       <c r="I251" s="59">
-        <f ca="1">I256*I34</f>
+        <f>I256*I34</f>
         <v>0</v>
       </c>
       <c r="J251" s="59">
-        <f ca="1">J256*J34</f>
+        <f>J256*J34</f>
         <v>0</v>
       </c>
       <c r="K251" s="59">
-        <f ca="1">K256*K34</f>
+        <f>K256*K34</f>
         <v>0</v>
       </c>
     </row>
     <row r="252" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C252" s="17" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D252" s="61">
         <v>-21272126</v>
@@ -10165,7 +10165,7 @@
     </row>
     <row r="253" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C253" s="17" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="D253" s="59">
         <f>D111</f>
@@ -10180,23 +10180,23 @@
         <v>-5551093</v>
       </c>
       <c r="G253" s="59">
-        <f ca="1">SUM(G250:G252)</f>
+        <f>SUM(G250:G252)</f>
         <v>-5551093</v>
       </c>
       <c r="H253" s="59">
-        <f ca="1">SUM(H250:H252)</f>
+        <f>SUM(H250:H252)</f>
         <v>-5551093</v>
       </c>
       <c r="I253" s="59">
-        <f ca="1">SUM(I250:I252)</f>
+        <f>SUM(I250:I252)</f>
         <v>-5551093</v>
       </c>
       <c r="J253" s="59">
-        <f ca="1">SUM(J250:J252)</f>
+        <f>SUM(J250:J252)</f>
         <v>-5551093</v>
       </c>
       <c r="K253" s="59">
-        <f ca="1">SUM(K250:K252)</f>
+        <f>SUM(K250:K252)</f>
         <v>-5551093</v>
       </c>
     </row>
@@ -10212,7 +10212,7 @@
     </row>
     <row r="255" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C255" s="6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D255" s="1"/>
       <c r="E255" s="1">
@@ -10246,7 +10246,7 @@
     </row>
     <row r="256" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C256" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D256" s="22">
         <f>D251/D34</f>
@@ -10292,12 +10292,12 @@
     </row>
     <row r="258" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C258" s="13" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="259" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C259" s="47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D259" s="48">
         <f t="shared" ref="D259:K259" si="72">D$13</f>
@@ -10334,7 +10334,7 @@
     </row>
     <row r="260" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C260" s="42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D260" s="86">
         <f t="shared" ref="D260:K260" si="73">D$14</f>
@@ -10381,7 +10381,7 @@
     </row>
     <row r="262" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C262" s="6" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="E262" s="59">
         <f t="shared" ref="E262:K262" si="74">D266</f>
@@ -10414,7 +10414,7 @@
     </row>
     <row r="263" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C263" s="17" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="D263" s="90">
         <v>623106746</v>
@@ -10449,7 +10449,7 @@
     </row>
     <row r="264" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C264" s="17" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="D264" s="61">
         <v>59014040</v>
@@ -10483,7 +10483,7 @@
     </row>
     <row r="265" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C265" s="17" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="D265" s="90">
         <v>-103883829</v>
@@ -10517,7 +10517,7 @@
     </row>
     <row r="266" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C266" s="6" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="D266" s="19">
         <f>D90+D99</f>
@@ -10554,7 +10554,7 @@
     </row>
     <row r="267" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C267" s="6" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="D267" s="101">
         <f>D90/D266</f>
@@ -10601,7 +10601,7 @@
     </row>
     <row r="269" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C269" s="6" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="D269" s="22">
         <f>D263/D$18</f>
@@ -10638,7 +10638,7 @@
     </row>
     <row r="270" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C270" s="6" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D270" s="22"/>
       <c r="E270" s="22">
@@ -10672,7 +10672,7 @@
     </row>
     <row r="271" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C271" s="6" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="D271" s="22"/>
       <c r="E271" s="22">
@@ -10706,12 +10706,12 @@
     </row>
     <row r="273" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C273" s="13" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="274" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C274" s="47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D274" s="48">
         <f t="shared" ref="D274:K274" si="76">D$13</f>
@@ -10748,7 +10748,7 @@
     </row>
     <row r="275" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C275" s="42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D275" s="86">
         <f t="shared" ref="D275:K275" si="77">D$14</f>
@@ -10796,7 +10796,7 @@
     </row>
     <row r="277" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C277" s="6" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="D277" s="19"/>
       <c r="E277" s="59">
@@ -10830,7 +10830,7 @@
     </row>
     <row r="278" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C278" s="17" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="D278" s="160">
         <v>223106746</v>
@@ -10864,7 +10864,7 @@
     </row>
     <row r="279" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C279" s="17" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D279" s="160">
         <v>-72874111</v>
@@ -10898,7 +10898,7 @@
     </row>
     <row r="280" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C280" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D280" s="19">
         <f>D71</f>
@@ -10945,7 +10945,7 @@
     </row>
     <row r="282" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C282" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D282" s="1">
         <f>D278/D18</f>
@@ -10982,7 +10982,7 @@
     </row>
     <row r="283" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C283" s="6" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="D283" s="1"/>
       <c r="E283" s="1">
@@ -11016,12 +11016,12 @@
     </row>
     <row r="285" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C285" s="13" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="286" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C286" s="47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D286" s="48">
         <f t="shared" ref="D286:K286" si="80">D$13</f>
@@ -11058,7 +11058,7 @@
     </row>
     <row r="287" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C287" s="42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D287" s="86">
         <f t="shared" ref="D287:K287" si="81">D$14</f>
@@ -11095,7 +11095,7 @@
     </row>
     <row r="289" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C289" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D289" s="19"/>
       <c r="E289" s="59">
@@ -11129,7 +11129,7 @@
     </row>
     <row r="290" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C290" s="17" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="D290" s="90"/>
       <c r="E290" s="61">
@@ -11162,7 +11162,7 @@
     </row>
     <row r="291" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C291" s="17" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="D291" s="90"/>
       <c r="E291" s="61">
@@ -11194,7 +11194,7 @@
     </row>
     <row r="292" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C292" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="D292" s="19">
         <f>D73</f>
@@ -11241,7 +11241,7 @@
     </row>
     <row r="294" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C294" s="6" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="D294" s="1"/>
       <c r="E294" s="1">
@@ -11274,7 +11274,7 @@
     </row>
     <row r="295" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C295" s="6" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="D295" s="1"/>
       <c r="E295" s="1">
@@ -11308,16 +11308,16 @@
     </row>
     <row r="297" spans="3:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C297" s="13" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="D297" s="258"/>
       <c r="N297" s="13" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="298" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C298" s="47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D298" s="48">
         <f t="shared" ref="D298:K298" si="84">D$13</f>
@@ -11352,21 +11352,21 @@
         <v>2030</v>
       </c>
       <c r="N298" s="6" t="s">
+        <v>239</v>
+      </c>
+      <c r="O298" s="6" t="s">
         <v>240</v>
       </c>
-      <c r="O298" s="6" t="s">
+      <c r="P298" s="6" t="s">
         <v>241</v>
       </c>
-      <c r="P298" s="6" t="s">
+      <c r="Q298" s="6" t="s">
         <v>242</v>
-      </c>
-      <c r="Q298" s="6" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="299" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C299" s="42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D299" s="86">
         <f t="shared" ref="D299:K299" si="85">D$14</f>
@@ -11431,10 +11431,10 @@
     </row>
     <row r="301" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C301" s="6" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D301" s="97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N301" s="273">
         <v>45357</v>
@@ -11452,7 +11452,7 @@
     </row>
     <row r="303" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C303" s="6" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D303" s="73"/>
       <c r="E303" s="260">
@@ -11498,7 +11498,7 @@
     </row>
     <row r="304" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C304" s="6" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D304" s="73"/>
       <c r="E304" s="260">
@@ -11544,7 +11544,7 @@
     </row>
     <row r="305" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C305" s="6" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="D305" s="73"/>
       <c r="E305" s="255">
@@ -11591,7 +11591,7 @@
     </row>
     <row r="306" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C306" s="6" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="E306" s="255">
         <f>-E19/E317</f>
@@ -11652,7 +11652,7 @@
     </row>
     <row r="308" spans="3:17" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C308" s="13" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="D308" s="258"/>
       <c r="N308" s="273">
@@ -11671,7 +11671,7 @@
     </row>
     <row r="309" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C309" s="6" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="D309" s="59"/>
       <c r="E309" s="59"/>
@@ -11699,7 +11699,7 @@
     </row>
     <row r="310" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C310" s="6" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="D310" s="59"/>
       <c r="E310" s="59"/>
@@ -11724,7 +11724,7 @@
     </row>
     <row r="311" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C311" s="6" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="D311" s="59"/>
       <c r="E311" s="59"/>
@@ -11765,7 +11765,7 @@
     </row>
     <row r="313" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C313" s="6" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="D313" s="59"/>
       <c r="E313" s="59"/>
@@ -11775,53 +11775,53 @@
         <v>24205423454</v>
       </c>
       <c r="H313" s="59">
-        <f ca="1">G315</f>
-        <v>27824542844.227249</v>
+        <f>G315</f>
+        <v>27615874858.155228</v>
       </c>
       <c r="I313" s="59">
-        <f ca="1">H315</f>
-        <v>30347405497.232681</v>
+        <f>H315</f>
+        <v>29894688248.070747</v>
       </c>
       <c r="J313" s="59">
-        <f ca="1">I315</f>
-        <v>32809919771.241344</v>
+        <f>I315</f>
+        <v>32155317046.922569</v>
       </c>
       <c r="K313" s="59">
-        <f ca="1">J315</f>
-        <v>34038777423.796741</v>
+        <f>J315</f>
+        <v>33234299062.961876</v>
       </c>
     </row>
     <row r="314" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C314" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="D314" s="59"/>
       <c r="E314" s="59"/>
       <c r="F314" s="59"/>
       <c r="G314" s="59">
-        <f ca="1">G334</f>
-        <v>3619119390.2272496</v>
+        <f>G334</f>
+        <v>3410451404.1552277</v>
       </c>
       <c r="H314" s="59">
-        <f ca="1">H334</f>
-        <v>2522862653.005434</v>
+        <f>H334</f>
+        <v>2278813389.9155216</v>
       </c>
       <c r="I314" s="59">
-        <f ca="1">I334</f>
-        <v>2462514274.0086641</v>
+        <f>I334</f>
+        <v>2260628798.8518205</v>
       </c>
       <c r="J314" s="59">
-        <f ca="1">J334</f>
-        <v>1228857652.5553963</v>
+        <f>J334</f>
+        <v>1078982016.0393066</v>
       </c>
       <c r="K314" s="59">
-        <f ca="1">K334</f>
-        <v>764411662.85628676</v>
+        <f>K334</f>
+        <v>618440479.04412365</v>
       </c>
     </row>
     <row r="315" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C315" s="6" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="D315" s="59"/>
       <c r="E315" s="59"/>
@@ -11830,29 +11830,29 @@
         <v>24205423454</v>
       </c>
       <c r="G315" s="59">
-        <f ca="1">G313+G314</f>
-        <v>27824542844.227249</v>
+        <f>G313+G314</f>
+        <v>27615874858.155228</v>
       </c>
       <c r="H315" s="59">
-        <f ca="1">H313+H314</f>
-        <v>30347405497.232681</v>
+        <f>H313+H314</f>
+        <v>29894688248.070747</v>
       </c>
       <c r="I315" s="59">
-        <f ca="1">I313+I314</f>
-        <v>32809919771.241344</v>
+        <f>I313+I314</f>
+        <v>32155317046.922569</v>
       </c>
       <c r="J315" s="59">
-        <f ca="1">J313+J314</f>
-        <v>34038777423.796741</v>
+        <f>J313+J314</f>
+        <v>33234299062.961876</v>
       </c>
       <c r="K315" s="59">
-        <f ca="1">K313+K314</f>
-        <v>34803189086.65303</v>
+        <f>K313+K314</f>
+        <v>33852739542.006001</v>
       </c>
     </row>
     <row r="316" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C316" s="6" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D316" s="18">
         <f>D85+D86+D95+D96+D97</f>
@@ -11867,29 +11867,29 @@
         <v>26694573624</v>
       </c>
       <c r="G316" s="18">
-        <f ca="1">G311+G315+G97</f>
-        <v>28224774556.227249</v>
+        <f>G311+G315+G97</f>
+        <v>28016106570.155228</v>
       </c>
       <c r="H316" s="18">
-        <f ca="1">H311+H315+H97</f>
-        <v>30747637209.232681</v>
+        <f>H311+H315+H97</f>
+        <v>30294919960.070747</v>
       </c>
       <c r="I316" s="18">
-        <f ca="1">I311+I315+I97</f>
-        <v>32809919771.241344</v>
+        <f>I311+I315+I97</f>
+        <v>32155317046.922569</v>
       </c>
       <c r="J316" s="18">
-        <f ca="1">J311+J315+J97</f>
-        <v>34038777423.796741</v>
+        <f>J311+J315+J97</f>
+        <v>33234299062.961876</v>
       </c>
       <c r="K316" s="18">
-        <f ca="1">K311+K315+K97</f>
-        <v>34803189086.65303</v>
+        <f>K311+K315+K97</f>
+        <v>33852739542.006001</v>
       </c>
     </row>
     <row r="317" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C317" s="6" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D317" s="59"/>
       <c r="E317" s="59">
@@ -11901,29 +11901,29 @@
         <v>23540518025.5</v>
       </c>
       <c r="G317" s="59">
-        <f ca="1">IF($D$301=1,IFERROR(AVERAGE(F316,G316),F316),F316)</f>
-        <v>27459674090.113625</v>
+        <f>IF($D$301=1,IFERROR(AVERAGE(F316,G316),F316),F316)</f>
+        <v>26694573624</v>
       </c>
       <c r="H317" s="59">
-        <f ca="1">IF($D$301=1,IFERROR(AVERAGE(G316,H316),G316),G316)</f>
-        <v>29486205882.729965</v>
+        <f>IF($D$301=1,IFERROR(AVERAGE(G316,H316),G316),G316)</f>
+        <v>28016106570.155228</v>
       </c>
       <c r="I317" s="59">
-        <f ca="1">IF($D$301=1,IFERROR(AVERAGE(H316,I316),H316),H316)</f>
-        <v>31778778490.237015</v>
+        <f>IF($D$301=1,IFERROR(AVERAGE(H316,I316),H316),H316)</f>
+        <v>30294919960.070747</v>
       </c>
       <c r="J317" s="59">
-        <f ca="1">IF($D$301=1,IFERROR(AVERAGE(I316,J316),I316),I316)</f>
-        <v>33424348597.519043</v>
+        <f>IF($D$301=1,IFERROR(AVERAGE(I316,J316),I316),I316)</f>
+        <v>32155317046.922569</v>
       </c>
       <c r="K317" s="59">
-        <f ca="1">IF($D$301=1,IFERROR(AVERAGE(J316,K316),J316),J316)</f>
-        <v>34420983255.224884</v>
+        <f>IF($D$301=1,IFERROR(AVERAGE(J316,K316),J316),J316)</f>
+        <v>33234299062.961876</v>
       </c>
     </row>
     <row r="318" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C318" s="6" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="D318" s="59">
         <f t="shared" ref="D318:K318" si="87">D306*D317</f>
@@ -11938,29 +11938,29 @@
         <v>6963884903</v>
       </c>
       <c r="G318" s="59">
-        <f t="shared" ca="1" si="87"/>
-        <v>6756494037.6363268</v>
+        <f t="shared" si="87"/>
+        <v>6568239919.2325459</v>
       </c>
       <c r="H318" s="59">
-        <f t="shared" ca="1" si="87"/>
-        <v>7218772371.2625799</v>
+        <f t="shared" si="87"/>
+        <v>6858864679.4139566</v>
       </c>
       <c r="I318" s="59">
-        <f t="shared" ca="1" si="87"/>
-        <v>7780036844.0131531</v>
+        <f t="shared" si="87"/>
+        <v>7416760639.4370899</v>
       </c>
       <c r="J318" s="59">
-        <f t="shared" ca="1" si="87"/>
-        <v>8182903054.4936485</v>
+        <f t="shared" si="87"/>
+        <v>7872220495.6001749</v>
       </c>
       <c r="K318" s="59">
-        <f t="shared" ca="1" si="87"/>
-        <v>8426897780.7023354</v>
+        <f t="shared" si="87"/>
+        <v>8136375388.8221512</v>
       </c>
     </row>
     <row r="319" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C319" s="6" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="D319" s="73">
         <f t="shared" ref="D319:K319" si="88">D318/D172</f>
@@ -11975,29 +11975,29 @@
         <v>0.70393414461570136</v>
       </c>
       <c r="G319" s="73">
-        <f t="shared" ca="1" si="88"/>
-        <v>0.75344962388894998</v>
+        <f t="shared" si="88"/>
+        <v>0.73245648840821542</v>
       </c>
       <c r="H319" s="73">
-        <f t="shared" ca="1" si="88"/>
-        <v>0.71476413919916126</v>
+        <f t="shared" si="88"/>
+        <v>0.67912800907550908</v>
       </c>
       <c r="I319" s="73">
-        <f t="shared" ca="1" si="88"/>
-        <v>0.69076448563951087</v>
+        <f t="shared" si="88"/>
+        <v>0.65851035810383496</v>
       </c>
       <c r="J319" s="73">
-        <f t="shared" ca="1" si="88"/>
-        <v>0.66249084125306013</v>
+        <f t="shared" si="88"/>
+        <v>0.6373378670050075</v>
       </c>
       <c r="K319" s="73">
-        <f t="shared" ca="1" si="88"/>
-        <v>0.62896014781518428</v>
+        <f t="shared" si="88"/>
+        <v>0.60727636674938945</v>
       </c>
     </row>
     <row r="320" spans="3:17" x14ac:dyDescent="0.25">
       <c r="C320" s="6" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D320" s="73"/>
       <c r="E320" s="73">
@@ -12013,20 +12013,20 @@
         <v>0.39128564955697387</v>
       </c>
       <c r="H320" s="73">
-        <f t="shared" ca="1" si="89"/>
-        <v>0.39128564955697387</v>
+        <f t="shared" si="89"/>
+        <v>0.39128564955697392</v>
       </c>
       <c r="I320" s="73">
-        <f t="shared" ca="1" si="89"/>
-        <v>0.39128564955697387</v>
+        <f t="shared" si="89"/>
+        <v>0.39128564955697392</v>
       </c>
       <c r="J320" s="73">
-        <f t="shared" ca="1" si="89"/>
-        <v>0.39128564955697381</v>
+        <f t="shared" si="89"/>
+        <v>0.39128564955697392</v>
       </c>
       <c r="K320" s="73">
-        <f t="shared" ca="1" si="89"/>
-        <v>0.39128564955697381</v>
+        <f t="shared" si="89"/>
+        <v>0.39128564955697392</v>
       </c>
     </row>
     <row r="321" spans="3:11" x14ac:dyDescent="0.25">
@@ -12041,63 +12041,63 @@
     </row>
     <row r="322" spans="3:11" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C322" s="13" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="D322" s="258"/>
     </row>
     <row r="323" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C323" s="6" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="G323" s="27">
         <f>F335</f>
         <v>3458917393</v>
       </c>
       <c r="H323" s="27">
-        <f ca="1">G335</f>
+        <f>G335</f>
         <v>1866746452.704</v>
       </c>
       <c r="I323" s="27">
-        <f ca="1">H335</f>
-        <v>1937135695.5864532</v>
+        <f>H335</f>
+        <v>1927536968.2271404</v>
       </c>
       <c r="J323" s="27">
-        <f ca="1">I335</f>
-        <v>2053187377.6247032</v>
+        <f>I335</f>
+        <v>2032362384.1632543</v>
       </c>
       <c r="K323" s="27">
-        <f ca="1">J335</f>
-        <v>2148052375.4771018</v>
+        <f>J335</f>
+        <v>2117940650.1584382</v>
       </c>
     </row>
     <row r="324" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C324" s="6" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="G324" s="256">
-        <f ca="1">G131</f>
-        <v>-1677563293.5874677</v>
+        <f>G131</f>
+        <v>-1468895307.5154457</v>
       </c>
       <c r="H324" s="256">
-        <f ca="1">H131</f>
-        <v>-891083972.91663361</v>
+        <f>H131</f>
+        <v>-628144625.01151371</v>
       </c>
       <c r="I324" s="256">
-        <f ca="1">I131</f>
-        <v>-175516507.55458069</v>
+        <f>I131</f>
+        <v>59049212.828625679</v>
       </c>
       <c r="J324" s="256">
-        <f ca="1">J131</f>
-        <v>831737841.08416653</v>
+        <f>J131</f>
+        <v>1016693400.0177584</v>
       </c>
       <c r="K324" s="256">
-        <f ca="1">K131</f>
-        <v>1460200221.1968632</v>
+        <f>K131</f>
+        <v>1636999999.9516649</v>
       </c>
     </row>
     <row r="325" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C325" s="6" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="G325" s="256">
         <f>G136</f>
@@ -12122,57 +12122,57 @@
     </row>
     <row r="326" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C326" s="6" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="G326" s="256">
         <f>G139+G140+G310+G396</f>
         <v>-2748797142.9228702</v>
       </c>
       <c r="H326" s="256">
-        <f ca="1">H139+H140+H310+H396</f>
-        <v>-685565533.14810824</v>
+        <f>H139+H140+H310+H396</f>
+        <v>-714054345.3226285</v>
       </c>
       <c r="I326" s="256">
-        <f ca="1">I139+I140+I310+I396</f>
-        <v>-1205526073.7170608</v>
+        <f>I139+I140+I310+I396</f>
+        <v>-1249432585.0455596</v>
       </c>
       <c r="J326" s="256">
-        <f ca="1">J139+J140+J310+J396</f>
-        <v>-917629449.86481524</v>
+        <f>J139+J140+J310+J396</f>
+        <v>-961996104.13953185</v>
       </c>
       <c r="K326" s="256">
-        <f ca="1">K139+K140+K310+K396</f>
-        <v>-1036802512.6849163</v>
+        <f>K139+K140+K310+K396</f>
+        <v>-1074525386.9072952</v>
       </c>
     </row>
     <row r="327" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C327" s="6" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="G327" s="27">
-        <f ca="1">SUM(G323:G326)</f>
-        <v>-1752372937.5232496</v>
+        <f>SUM(G323:G326)</f>
+        <v>-1543704951.4512277</v>
       </c>
       <c r="H327" s="27">
-        <f ca="1">SUM(H323:H326)</f>
-        <v>-585726957.41898084</v>
+        <f>SUM(H323:H326)</f>
+        <v>-351276421.6883812</v>
       </c>
       <c r="I327" s="27">
-        <f ca="1">SUM(I323:I326)</f>
-        <v>-409326896.38396096</v>
+        <f>SUM(I323:I326)</f>
+        <v>-228266414.68856621</v>
       </c>
       <c r="J327" s="27">
-        <f ca="1">SUM(J323:J326)</f>
-        <v>919194722.92170548</v>
+        <f>SUM(J323:J326)</f>
+        <v>1038958634.1191316</v>
       </c>
       <c r="K327" s="27">
-        <f ca="1">SUM(K323:K326)</f>
-        <v>1440168164.6383631</v>
+        <f>SUM(K323:K326)</f>
+        <v>1549133343.8521223</v>
       </c>
     </row>
     <row r="328" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C328" s="6" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="F328" s="61">
         <v>638796066</v>
@@ -12200,7 +12200,7 @@
     </row>
     <row r="329" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C329" s="6" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G329" s="257">
         <v>4.5999999999999999E-2</v>
@@ -12224,107 +12224,107 @@
     </row>
     <row r="330" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C330" s="6" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G330" s="59">
         <f>G328+G329*F316</f>
         <v>1866746452.704</v>
       </c>
       <c r="H330" s="59">
-        <f ca="1">H328+H329*G316</f>
-        <v>1937135695.5864534</v>
+        <f>H328+H329*G316</f>
+        <v>1927536968.2271404</v>
       </c>
       <c r="I330" s="59">
-        <f ca="1">I328+I329*H316</f>
-        <v>2053187377.6247034</v>
+        <f>I328+I329*H316</f>
+        <v>2032362384.1632543</v>
       </c>
       <c r="J330" s="59">
-        <f ca="1">J328+J329*I316</f>
-        <v>2148052375.4771018</v>
+        <f>J328+J329*I316</f>
+        <v>2117940650.1584382</v>
       </c>
       <c r="K330" s="59">
-        <f ca="1">K328+K329*J316</f>
-        <v>2204579827.4946499</v>
+        <f>K328+K329*J316</f>
+        <v>2167573822.896246</v>
       </c>
     </row>
     <row r="331" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C331" s="6" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G331" s="59">
-        <f ca="1">G330-G327</f>
-        <v>3619119390.2272496</v>
+        <f>G330-G327</f>
+        <v>3410451404.1552277</v>
       </c>
       <c r="H331" s="59">
-        <f ca="1">H330-H327</f>
-        <v>2522862653.005434</v>
+        <f>H330-H327</f>
+        <v>2278813389.9155216</v>
       </c>
       <c r="I331" s="59">
-        <f ca="1">I330-I327</f>
-        <v>2462514274.0086641</v>
+        <f>I330-I327</f>
+        <v>2260628798.8518205</v>
       </c>
       <c r="J331" s="59">
-        <f ca="1">J330-J327</f>
-        <v>1228857652.5553963</v>
+        <f>J330-J327</f>
+        <v>1078982016.0393066</v>
       </c>
       <c r="K331" s="59">
-        <f ca="1">K330-K327</f>
-        <v>764411662.85628676</v>
+        <f>K330-K327</f>
+        <v>618440479.04412365</v>
       </c>
     </row>
     <row r="332" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C332" s="6" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G332" s="59">
         <f>-G313</f>
         <v>-24205423454</v>
       </c>
       <c r="H332" s="59">
-        <f ca="1">-H313</f>
-        <v>-27824542844.227249</v>
+        <f>-H313</f>
+        <v>-27615874858.155228</v>
       </c>
       <c r="I332" s="59">
-        <f ca="1">-I313</f>
-        <v>-30347405497.232681</v>
+        <f>-I313</f>
+        <v>-29894688248.070747</v>
       </c>
       <c r="J332" s="59">
-        <f ca="1">-J313</f>
-        <v>-32809919771.241344</v>
+        <f>-J313</f>
+        <v>-32155317046.922569</v>
       </c>
       <c r="K332" s="59">
-        <f ca="1">-K313</f>
-        <v>-34038777423.796741</v>
+        <f>-K313</f>
+        <v>-33234299062.961876</v>
       </c>
     </row>
     <row r="334" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C334" s="6" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G334" s="18">
-        <f ca="1">MAX(G331,G332)</f>
-        <v>3619119390.2272496</v>
+        <f>MAX(G331,G332)</f>
+        <v>3410451404.1552277</v>
       </c>
       <c r="H334" s="18">
-        <f ca="1">MAX(H331,H332)</f>
-        <v>2522862653.005434</v>
+        <f>MAX(H331,H332)</f>
+        <v>2278813389.9155216</v>
       </c>
       <c r="I334" s="18">
-        <f ca="1">MAX(I331,I332)</f>
-        <v>2462514274.0086641</v>
+        <f>MAX(I331,I332)</f>
+        <v>2260628798.8518205</v>
       </c>
       <c r="J334" s="18">
-        <f ca="1">MAX(J331,J332)</f>
-        <v>1228857652.5553963</v>
+        <f>MAX(J331,J332)</f>
+        <v>1078982016.0393066</v>
       </c>
       <c r="K334" s="18">
-        <f ca="1">MAX(K331,K332)</f>
-        <v>764411662.85628676</v>
+        <f>MAX(K331,K332)</f>
+        <v>618440479.04412365</v>
       </c>
     </row>
     <row r="335" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C335" s="6" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="D335" s="27"/>
       <c r="E335" s="27"/>
@@ -12333,54 +12333,54 @@
         <v>3458917393</v>
       </c>
       <c r="G335" s="27">
-        <f ca="1">G327+G334</f>
+        <f>G327+G334</f>
         <v>1866746452.704</v>
       </c>
       <c r="H335" s="27">
-        <f ca="1">H327+H334</f>
-        <v>1937135695.5864532</v>
+        <f>H327+H334</f>
+        <v>1927536968.2271404</v>
       </c>
       <c r="I335" s="27">
-        <f ca="1">I327+I334</f>
-        <v>2053187377.6247032</v>
+        <f>I327+I334</f>
+        <v>2032362384.1632543</v>
       </c>
       <c r="J335" s="27">
-        <f ca="1">J327+J334</f>
-        <v>2148052375.4771018</v>
+        <f>J327+J334</f>
+        <v>2117940650.1584382</v>
       </c>
       <c r="K335" s="27">
-        <f ca="1">K327+K334</f>
-        <v>2204579827.4946499</v>
+        <f>K327+K334</f>
+        <v>2167573822.896246</v>
       </c>
     </row>
     <row r="337" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C337" s="6" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G337" s="27">
-        <f ca="1">G338-G315</f>
-        <v>1775457155.7727509</v>
+        <f>G338-G315</f>
+        <v>1984125141.8447723</v>
       </c>
       <c r="H337" s="27">
-        <f ca="1">H338-H315</f>
-        <v>-747405497.23268127</v>
+        <f>H338-H315</f>
+        <v>-294688248.07074738</v>
       </c>
       <c r="I337" s="27">
-        <f ca="1">I338-I315</f>
-        <v>-3209919771.2413445</v>
+        <f>I338-I315</f>
+        <v>-2555317046.9225693</v>
       </c>
       <c r="J337" s="27">
-        <f ca="1">J338-J315</f>
-        <v>-4438777423.7967415</v>
+        <f>J338-J315</f>
+        <v>-3634299062.9618759</v>
       </c>
       <c r="K337" s="27">
-        <f ca="1">K338-K315</f>
-        <v>-5203189086.6530304</v>
+        <f>K338-K315</f>
+        <v>-4252739542.0060005</v>
       </c>
     </row>
     <row r="338" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C338" s="6" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="F338" s="61">
         <v>29600000000</v>
@@ -12408,62 +12408,62 @@
     </row>
     <row r="339" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C339" s="6" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G339" s="27">
-        <f ca="1">G335-G146</f>
+        <f>G335-G146</f>
         <v>0</v>
       </c>
       <c r="H339" s="27">
-        <f ca="1">H335-H146</f>
+        <f>H335-H146</f>
         <v>0</v>
       </c>
       <c r="I339" s="27">
-        <f ca="1">I335-I146</f>
+        <f>I335-I146</f>
         <v>0</v>
       </c>
       <c r="J339" s="27">
-        <f ca="1">J335-J146</f>
+        <f>J335-J146</f>
         <v>0</v>
       </c>
       <c r="K339" s="27">
-        <f ca="1">K335-K146</f>
+        <f>K335-K146</f>
         <v>0</v>
       </c>
     </row>
     <row r="340" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C340" s="6" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G340" s="73">
-        <f ca="1">(G316+G88+G89+G97-G66)/((G316+G88+G89+G97-G66)+G112)</f>
-        <v>0.72996169982980197</v>
+        <f>(G316+G88+G89+G97-G66)/((G316+G88+G89+G97-G66)+G112)</f>
+        <v>0.72583695891790512</v>
       </c>
       <c r="H340" s="73">
-        <f ca="1">(H316+H88+H89+H97-H66)/((H316+H88+H89+H97-H66)+H112)</f>
-        <v>0.70970557297674008</v>
+        <f>(H316+H88+H89+H97-H66)/((H316+H88+H89+H97-H66)+H112)</f>
+        <v>0.70130789637244784</v>
       </c>
       <c r="I340" s="73">
-        <f ca="1">(I316+I88+I89+I97-I66)/((I316+I88+I89+I97-I66)+I112)</f>
-        <v>0.68554516510495622</v>
+        <f>(I316+I88+I89+I97-I66)/((I316+I88+I89+I97-I66)+I112)</f>
+        <v>0.67410035532037316</v>
       </c>
       <c r="J340" s="73">
-        <f ca="1">(J316+J88+J89+J97-J66)/((J316+J88+J89+J97-J66)+J112)</f>
-        <v>0.65586628372295241</v>
+        <f>(J316+J88+J89+J97-J66)/((J316+J88+J89+J97-J66)+J112)</f>
+        <v>0.64252938593001896</v>
       </c>
       <c r="K340" s="73">
-        <f ca="1">(K316+K88+K89+K97-K66)/((K316+K88+K89+K97-K66)+K112)</f>
-        <v>0.62261992268633937</v>
+        <f>(K316+K88+K89+K97-K66)/((K316+K88+K89+K97-K66)+K112)</f>
+        <v>0.60780430603508673</v>
       </c>
     </row>
     <row r="342" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C342" s="13" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="343" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C343" s="47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D343" s="48">
         <f t="shared" ref="D343:K343" si="90">D$13</f>
@@ -12500,7 +12500,7 @@
     </row>
     <row r="344" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C344" s="42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D344" s="86">
         <f t="shared" ref="D344:K344" si="91">D$14</f>
@@ -12537,7 +12537,7 @@
     </row>
     <row r="346" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C346" s="6" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="D346" s="59"/>
       <c r="E346" s="59">
@@ -12571,7 +12571,7 @@
     </row>
     <row r="347" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C347" s="6" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="D347" s="61"/>
       <c r="E347" s="61">
@@ -12605,7 +12605,7 @@
     </row>
     <row r="348" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C348" s="6" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="D348" s="61"/>
       <c r="E348" s="61">
@@ -12639,7 +12639,7 @@
     </row>
     <row r="349" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C349" s="6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D349" s="61"/>
       <c r="E349" s="61">
@@ -12671,7 +12671,7 @@
     </row>
     <row r="350" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C350" s="6" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="D350" s="61"/>
       <c r="E350" s="170">
@@ -12705,7 +12705,7 @@
     </row>
     <row r="351" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C351" s="6" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="D351" s="59">
         <f>D65+D74</f>
@@ -12742,7 +12742,7 @@
     </row>
     <row r="352" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C352" s="6" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="D352" s="73">
         <f>D65/D351</f>
@@ -12779,7 +12779,7 @@
     </row>
     <row r="354" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C354" s="6" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D354" s="73"/>
       <c r="E354" s="73"/>
@@ -12805,7 +12805,7 @@
     </row>
     <row r="355" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C355" s="6" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="D355" s="73"/>
       <c r="E355" s="73">
@@ -12839,7 +12839,7 @@
     </row>
     <row r="356" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C356" s="6" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="D356" s="73"/>
       <c r="E356" s="73">
@@ -12873,7 +12873,7 @@
     </row>
     <row r="357" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C357" s="6" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="D357" s="73"/>
       <c r="E357" s="73">
@@ -12907,7 +12907,7 @@
     </row>
     <row r="358" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C358" s="6" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D358" s="73"/>
       <c r="E358" s="73">
@@ -12941,7 +12941,7 @@
     </row>
     <row r="359" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C359" s="6" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E359" s="73">
         <f>E172/AVERAGE(D351,E351)</f>
@@ -12974,7 +12974,7 @@
     </row>
     <row r="360" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C360" s="6" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="E360" s="1">
         <f>E359-E303</f>
@@ -13007,12 +13007,12 @@
     </row>
     <row r="361" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C361" s="13" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
     </row>
     <row r="362" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C362" s="47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D362" s="48">
         <f t="shared" ref="D362:K362" si="96">D$13</f>
@@ -13049,7 +13049,7 @@
     </row>
     <row r="363" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C363" s="42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D363" s="86">
         <f t="shared" ref="D363:K363" si="97">D$14</f>
@@ -13086,7 +13086,7 @@
     </row>
     <row r="365" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C365" s="6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D365" s="59"/>
       <c r="E365" s="61">
@@ -13118,7 +13118,7 @@
     </row>
     <row r="366" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C366" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D366" s="73"/>
       <c r="E366" s="73">
@@ -13152,7 +13152,7 @@
     </row>
     <row r="367" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C367" s="6" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D367" s="27"/>
       <c r="E367" s="27">
@@ -13186,7 +13186,7 @@
     </row>
     <row r="368" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C368" s="6" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="E368" s="73">
         <f>E367/E18</f>
@@ -13219,7 +13219,7 @@
     </row>
     <row r="369" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C369" s="6" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="E369" s="59">
         <f t="shared" ref="E369:K369" si="98">E365+E367</f>
@@ -13252,7 +13252,7 @@
     </row>
     <row r="371" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C371" s="6" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E371" s="61">
         <v>708846873</v>
@@ -13283,7 +13283,7 @@
     </row>
     <row r="372" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C372" s="6" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D372" s="73"/>
       <c r="E372" s="73">
@@ -13317,7 +13317,7 @@
     </row>
     <row r="373" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C373" s="6" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="E373" s="61">
         <f>E88-E371</f>
@@ -13350,7 +13350,7 @@
     </row>
     <row r="374" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C374" s="6" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D374" s="73"/>
       <c r="E374" s="73">
@@ -13384,7 +13384,7 @@
     </row>
     <row r="375" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C375" s="6" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="E375" s="59">
         <f t="shared" ref="E375:K375" si="99">E371+E373</f>
@@ -13417,7 +13417,7 @@
     </row>
     <row r="377" spans="3:11" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C377" s="13" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="D377" s="258"/>
       <c r="F377" s="259"/>
@@ -13425,7 +13425,7 @@
     </row>
     <row r="378" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C378" s="6" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F378" s="61">
         <v>515659966</v>
@@ -13453,7 +13453,7 @@
     </row>
     <row r="379" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C379" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F379" s="61">
         <v>36923005</v>
@@ -13481,7 +13481,7 @@
     </row>
     <row r="380" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C380" s="6" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="F380" s="74">
         <v>0.2</v>
@@ -13509,7 +13509,7 @@
     </row>
     <row r="381" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C381" s="6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="F381" s="59">
         <f>F73-F379</f>
@@ -13546,13 +13546,13 @@
     </row>
     <row r="383" spans="3:11" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C383" s="63" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="D383" s="258"/>
     </row>
     <row r="384" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C384" s="6" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E384" s="1">
         <f>E385/-E46</f>
@@ -13585,7 +13585,7 @@
     </row>
     <row r="385" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C385" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E385" s="61">
         <v>88829420</v>
@@ -13616,7 +13616,7 @@
     </row>
     <row r="387" spans="3:11" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="C387" s="13" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="D387" s="40"/>
       <c r="E387" s="40"/>
@@ -13629,7 +13629,7 @@
     </row>
     <row r="388" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C388" s="47" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D388" s="48">
         <f t="shared" ref="D388:K388" si="101">D$13</f>
@@ -13666,7 +13666,7 @@
     </row>
     <row r="389" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C389" s="42" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D389" s="86">
         <f t="shared" ref="D389:K389" si="102">D$14</f>
@@ -13703,7 +13703,7 @@
     </row>
     <row r="391" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C391" s="6" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D391" s="61"/>
       <c r="E391" s="61">
@@ -13734,7 +13734,7 @@
     </row>
     <row r="392" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C392" s="6" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="D392" s="61"/>
       <c r="E392" s="61">
@@ -13766,7 +13766,7 @@
     </row>
     <row r="393" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C393" s="6" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D393" s="61"/>
       <c r="E393" s="61"/>
@@ -13793,7 +13793,7 @@
     </row>
     <row r="394" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C394" s="6" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="D394" s="61"/>
       <c r="E394" s="170">
@@ -13827,7 +13827,7 @@
     </row>
     <row r="395" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C395" s="6" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="D395" s="61"/>
       <c r="E395" s="73">
@@ -13845,7 +13845,7 @@
     </row>
     <row r="396" spans="3:11" x14ac:dyDescent="0.25">
       <c r="C396" s="6" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="G396" s="276">
         <v>0</v>
@@ -13978,8 +13978,8 @@
       </c>
       <c r="G7" s="52"/>
       <c r="H7" s="127">
-        <f ca="1">C49</f>
-        <v>4.8622683153514137</v>
+        <f>C49</f>
+        <v>5.0469089560442457</v>
       </c>
       <c r="J7" s="131"/>
     </row>
@@ -13996,11 +13996,11 @@
         <v>12</v>
       </c>
       <c r="H8" s="73">
-        <f ca="1">H7/H5-1</f>
-        <v>-0.80154006876116679</v>
+        <f>H7/H5-1</f>
+        <v>-0.79400371607982667</v>
       </c>
       <c r="I8" s="178" t="str">
-        <f ca="1">IF(H8&gt;15%,"BUY",IF(H8&lt;-15%,"SELL","HOLD"))</f>
+        <f>IF(H8&gt;15%,"BUY",IF(H8&lt;-15%,"SELL","HOLD"))</f>
         <v>SELL</v>
       </c>
     </row>
@@ -14095,20 +14095,20 @@
         <v>9115750503</v>
       </c>
       <c r="F14" s="191">
-        <f ca="1">FSM!G110</f>
-        <v>10879314177.179352</v>
+        <f>FSM!G110</f>
+        <v>11029325677.73805</v>
       </c>
       <c r="G14" s="191">
-        <f ca="1">FSM!H110</f>
-        <v>13131871090.798656</v>
+        <f>FSM!H110</f>
+        <v>13484589155.400612</v>
       </c>
       <c r="H14" s="191">
-        <f ca="1">FSM!I110</f>
-        <v>15727183285.18198</v>
+        <f>FSM!I110</f>
+        <v>16269613156.472633</v>
       </c>
       <c r="I14" s="191">
-        <f ca="1">FSM!J110</f>
-        <v>18698942948.119873</v>
+        <f>FSM!J110</f>
+        <v>19395640805.738598</v>
       </c>
     </row>
     <row r="15" spans="2:10" x14ac:dyDescent="0.25">
@@ -14117,24 +14117,24 @@
       </c>
       <c r="D15" s="192"/>
       <c r="E15" s="191">
-        <f ca="1">FSM!G110</f>
-        <v>10879314177.179352</v>
+        <f>FSM!G110</f>
+        <v>11029325677.73805</v>
       </c>
       <c r="F15" s="191">
-        <f ca="1">FSM!H110</f>
-        <v>13131871090.798656</v>
+        <f>FSM!H110</f>
+        <v>13484589155.400612</v>
       </c>
       <c r="G15" s="191">
-        <f ca="1">FSM!I110</f>
-        <v>15727183285.18198</v>
+        <f>FSM!I110</f>
+        <v>16269613156.472633</v>
       </c>
       <c r="H15" s="191">
-        <f ca="1">FSM!J110</f>
-        <v>18698942948.119873</v>
+        <f>FSM!J110</f>
+        <v>19395640805.738598</v>
       </c>
       <c r="I15" s="191">
-        <f ca="1">FSM!K110</f>
-        <v>22165148152.323792</v>
+        <f>FSM!K110</f>
+        <v>23007060685.207199</v>
       </c>
     </row>
     <row r="16" spans="2:10" x14ac:dyDescent="0.25">
@@ -14147,24 +14147,24 @@
         <v>2018397923</v>
       </c>
       <c r="E16" s="191">
-        <f ca="1">FSM!G35</f>
-        <v>2016855214.1801429</v>
+        <f>FSM!G35</f>
+        <v>2166866714.738843</v>
       </c>
       <c r="F16" s="191">
-        <f ca="1">FSM!H35</f>
-        <v>2490498826.2428308</v>
+        <f>FSM!H35</f>
+        <v>2721694202.4606042</v>
       </c>
       <c r="G16" s="191">
-        <f ca="1">FSM!I35</f>
-        <v>2908362518.1367617</v>
+        <f>FSM!I35</f>
+        <v>3141980836.1539602</v>
       </c>
       <c r="H16" s="191">
-        <f ca="1">FSM!J35</f>
-        <v>3350470671.5003076</v>
+        <f>FSM!J35</f>
+        <v>3549105312.103096</v>
       </c>
       <c r="I16" s="191">
-        <f ca="1">FSM!K35</f>
-        <v>3915098385.4421186</v>
+        <f>FSM!K35</f>
+        <v>4098035934.9291773</v>
       </c>
     </row>
     <row r="17" spans="2:13" x14ac:dyDescent="0.25">
@@ -14173,24 +14173,24 @@
       </c>
       <c r="D17" s="58"/>
       <c r="E17" s="58">
-        <f ca="1">E16/D16-1</f>
-        <v>-7.6432342813959053E-4</v>
+        <f>E16/D16-1</f>
+        <v>7.3557741041553326E-2</v>
       </c>
       <c r="F17" s="58">
-        <f ca="1">F16/E16-1</f>
-        <v>0.23484264449554226</v>
+        <f>F16/E16-1</f>
+        <v>0.2560505839827949</v>
       </c>
       <c r="G17" s="58">
-        <f ca="1">G16/F16-1</f>
-        <v>0.167783131431674</v>
+        <f>G16/F16-1</f>
+        <v>0.15442096078001244</v>
       </c>
       <c r="H17" s="58">
-        <f ca="1">H16/G16-1</f>
-        <v>0.15201273933580395</v>
+        <f>H16/G16-1</f>
+        <v>0.12957573491997776</v>
       </c>
       <c r="I17" s="58">
-        <f ca="1">I16/H16-1</f>
-        <v>0.16852190909911058</v>
+        <f>I16/H16-1</f>
+        <v>0.15466732445332854</v>
       </c>
     </row>
     <row r="18" spans="2:13" x14ac:dyDescent="0.25">
@@ -14199,24 +14199,24 @@
       </c>
       <c r="D18" s="58"/>
       <c r="E18" s="278">
-        <f ca="1">E15-E14-FSM!G396</f>
-        <v>1763563674.1793518</v>
+        <f>E15-E14-FSM!G396</f>
+        <v>1913575174.7380505</v>
       </c>
       <c r="F18" s="278">
-        <f ca="1">F15-F14-FSM!H396</f>
-        <v>2252556913.6193047</v>
+        <f>F15-F14-FSM!H396</f>
+        <v>2455263477.6625614</v>
       </c>
       <c r="G18" s="278">
-        <f ca="1">G15-G14-FSM!I396</f>
-        <v>2595312194.3833237</v>
+        <f>G15-G14-FSM!I396</f>
+        <v>2785024001.0720215</v>
       </c>
       <c r="H18" s="278">
-        <f ca="1">H15-H14-FSM!J396</f>
-        <v>2971759662.9378929</v>
+        <f>H15-H14-FSM!J396</f>
+        <v>3126027649.2659645</v>
       </c>
       <c r="I18" s="278">
-        <f ca="1">I15-I14-FSM!K396</f>
-        <v>3466205204.2039185</v>
+        <f>I15-I14-FSM!K396</f>
+        <v>3611419879.4686012</v>
       </c>
     </row>
     <row r="19" spans="2:13" x14ac:dyDescent="0.25">
@@ -14225,24 +14225,24 @@
       </c>
       <c r="D19" s="58"/>
       <c r="E19" s="58">
-        <f ca="1">E18/E14</f>
-        <v>0.1934633548383056</v>
+        <f>E18/E14</f>
+        <v>0.20991965215681271</v>
       </c>
       <c r="F19" s="58">
-        <f ca="1">F18/F14</f>
-        <v>0.20704953243691676</v>
+        <f>F18/F14</f>
+        <v>0.22261229284564016</v>
       </c>
       <c r="G19" s="58">
-        <f ca="1">G18/G14</f>
-        <v>0.19763460792741314</v>
+        <f>G18/G14</f>
+        <v>0.20653384163036309</v>
       </c>
       <c r="H19" s="58">
-        <f ca="1">H18/H14</f>
-        <v>0.18895689132954022</v>
+        <f>H18/H14</f>
+        <v>0.19213902747419159</v>
       </c>
       <c r="I19" s="58">
-        <f ca="1">I18/I14</f>
-        <v>0.185369045395822</v>
+        <f>I18/I14</f>
+        <v>0.18619750260584783</v>
       </c>
     </row>
     <row r="20" spans="2:13" x14ac:dyDescent="0.25">
@@ -14295,24 +14295,24 @@
       </c>
       <c r="D23" s="58"/>
       <c r="E23" s="58">
-        <f ca="1">E19-E21</f>
-        <v>-8.8436645161694388E-2</v>
+        <f>E19-E21</f>
+        <v>-7.198034784318727E-2</v>
       </c>
       <c r="F23" s="58">
-        <f ca="1">F19-F21</f>
-        <v>-7.4850467563083223E-2</v>
+        <f>F19-F21</f>
+        <v>-5.9287707154359826E-2</v>
       </c>
       <c r="G23" s="58">
-        <f ca="1">G19-G21</f>
-        <v>-8.4265392072586848E-2</v>
+        <f>G19-G21</f>
+        <v>-7.5366158369636893E-2</v>
       </c>
       <c r="H23" s="58">
-        <f ca="1">H19-H21</f>
-        <v>-9.2943108670459768E-2</v>
+        <f>H19-H21</f>
+        <v>-8.9760972525808391E-2</v>
       </c>
       <c r="I23" s="58">
-        <f ca="1">I19-I21</f>
-        <v>-9.6530954604177988E-2</v>
+        <f>I19-I21</f>
+        <v>-9.5702497394152153E-2</v>
       </c>
     </row>
     <row r="24" spans="2:13" x14ac:dyDescent="0.25">
@@ -14334,20 +14334,20 @@
         <v>2569730066.7957001</v>
       </c>
       <c r="F25" s="195">
-        <f ca="1">F14*F21</f>
-        <v>3066878666.5468593</v>
+        <f>F14*F21</f>
+        <v>3109166908.5543561</v>
       </c>
       <c r="G25" s="195">
-        <f ca="1">G14*G21</f>
-        <v>3701874460.496141</v>
+        <f>G14*G21</f>
+        <v>3801305682.9074321</v>
       </c>
       <c r="H25" s="195">
-        <f ca="1">H14*H21</f>
-        <v>4433492968.0928001</v>
+        <f>H14*H21</f>
+        <v>4586403948.8096352</v>
       </c>
       <c r="I25" s="195">
-        <f ca="1">I14*I21</f>
-        <v>5271232017.0749922</v>
+        <f>I14*I21</f>
+        <v>5467631143.1377106</v>
       </c>
     </row>
     <row r="26" spans="2:13" x14ac:dyDescent="0.25">
@@ -14367,24 +14367,24 @@
       </c>
       <c r="D27" s="14"/>
       <c r="E27" s="14">
-        <f ca="1">E18-E25</f>
-        <v>-806166392.61634827</v>
+        <f>E18-E25</f>
+        <v>-656154892.05764961</v>
       </c>
       <c r="F27" s="14">
-        <f ca="1">F18-F25</f>
-        <v>-814321752.92755461</v>
+        <f>F18-F25</f>
+        <v>-653903430.89179468</v>
       </c>
       <c r="G27" s="14">
-        <f ca="1">G18-G25</f>
-        <v>-1106562266.1128173</v>
+        <f>G18-G25</f>
+        <v>-1016281681.8354106</v>
       </c>
       <c r="H27" s="14">
-        <f ca="1">H18-H25</f>
-        <v>-1461733305.1549072</v>
+        <f>H18-H25</f>
+        <v>-1460376299.5436707</v>
       </c>
       <c r="I27" s="14">
-        <f ca="1">I18-I25</f>
-        <v>-1805026812.8710737</v>
+        <f>I18-I25</f>
+        <v>-1856211263.6691093</v>
       </c>
       <c r="J27" s="202"/>
       <c r="K27" s="203"/>
@@ -14468,7 +14468,7 @@
     </row>
     <row r="32" spans="2:13" x14ac:dyDescent="0.25">
       <c r="B32" s="284" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C32" s="285">
         <f>D8</f>
@@ -14476,24 +14476,24 @@
       </c>
       <c r="D32" s="286"/>
       <c r="E32" s="287">
-        <f ca="1">E27</f>
-        <v>-806166392.61634827</v>
+        <f>E27</f>
+        <v>-656154892.05764961</v>
       </c>
       <c r="F32" s="287">
-        <f t="shared" ref="F32:I32" ca="1" si="0">F27</f>
-        <v>-814321752.92755461</v>
+        <f t="shared" ref="F32:I32" si="0">F27</f>
+        <v>-653903430.89179468</v>
       </c>
       <c r="G32" s="287">
-        <f t="shared" ca="1" si="0"/>
-        <v>-1106562266.1128173</v>
+        <f t="shared" si="0"/>
+        <v>-1016281681.8354106</v>
       </c>
       <c r="H32" s="287">
-        <f t="shared" ca="1" si="0"/>
-        <v>-1461733305.1549072</v>
+        <f t="shared" si="0"/>
+        <v>-1460376299.5436707</v>
       </c>
       <c r="I32" s="287">
-        <f t="shared" ca="1" si="0"/>
-        <v>-1805026812.8710737</v>
+        <f t="shared" si="0"/>
+        <v>-1856211263.6691093</v>
       </c>
       <c r="J32" s="210"/>
     </row>
@@ -14502,24 +14502,24 @@
         <v>35</v>
       </c>
       <c r="E33" s="211">
-        <f ca="1">E32/(1+$H$4)^((E31-$D$31)/365)</f>
-        <v>-628883994.55210876</v>
+        <f>E32/(1+$H$4)^((E31-$D$31)/365)</f>
+        <v>-511861215.42838722</v>
       </c>
       <c r="F33" s="211">
-        <f t="shared" ref="F33:I33" ca="1" si="1">F32/(1+$H$4)^((F31-$D$31)/365)</f>
-        <v>-495550297.45128036</v>
+        <f t="shared" ref="F33:I33" si="1">F32/(1+$H$4)^((F31-$D$31)/365)</f>
+        <v>-397928752.99951577</v>
       </c>
       <c r="G33" s="211">
-        <f t="shared" ca="1" si="1"/>
-        <v>-524949979.64639431</v>
+        <f t="shared" si="1"/>
+        <v>-482121128.22949862</v>
       </c>
       <c r="H33" s="211">
-        <f t="shared" ca="1" si="1"/>
-        <v>-540948675.01565337</v>
+        <f t="shared" si="1"/>
+        <v>-540446483.27876234</v>
       </c>
       <c r="I33" s="211">
-        <f t="shared" ca="1" si="1"/>
-        <v>-521095627.51608878</v>
+        <f t="shared" si="1"/>
+        <v>-535872135.71944577</v>
       </c>
     </row>
     <row r="34" spans="2:10" x14ac:dyDescent="0.25">
@@ -14555,8 +14555,8 @@
         <v>39</v>
       </c>
       <c r="C37" s="209">
-        <f ca="1">I27*(1+C36)</f>
-        <v>-1805026812.8710737</v>
+        <f>I27*(1+C36)</f>
+        <v>-1856211263.6691093</v>
       </c>
       <c r="E37" s="214"/>
     </row>
@@ -14586,8 +14586,8 @@
         <v>41</v>
       </c>
       <c r="C40" s="210">
-        <f ca="1">SUM(E33:I33)</f>
-        <v>-2711428574.1815257</v>
+        <f>SUM(E33:I33)</f>
+        <v>-2468229715.6556096</v>
       </c>
       <c r="E40" s="209"/>
     </row>
@@ -14597,8 +14597,8 @@
         <v>Equity value at 31 Dec 2025 (book value + PV of residual income)</v>
       </c>
       <c r="C41" s="215">
-        <f ca="1">D14+C40+C39</f>
-        <v>6404321928.8184738</v>
+        <f>D14+C40+C39</f>
+        <v>6647520787.3443909</v>
       </c>
       <c r="E41" s="215"/>
     </row>
@@ -14608,8 +14608,8 @@
         <v>Equity value at 12 Oct 2026 (rolled forward at Ke)</v>
       </c>
       <c r="C42" s="215">
-        <f ca="1">C41*(1+$H$4)^YEARFRAC($D$6,$D$7)</f>
-        <v>7779629304.5622616</v>
+        <f>C41*(1+$H$4)^YEARFRAC($D$6,$D$7)</f>
+        <v>8075054329.6707935</v>
       </c>
       <c r="E42" s="215"/>
     </row>
@@ -14618,8 +14618,8 @@
         <v>42</v>
       </c>
       <c r="C43" s="280">
-        <f ca="1">C42/D14</f>
-        <v>0.85342718649462601</v>
+        <f>C42/D14</f>
+        <v>0.88583538206901202</v>
       </c>
       <c r="E43" s="270"/>
     </row>
@@ -14645,8 +14645,8 @@
         <v>45</v>
       </c>
       <c r="C47" s="218">
-        <f ca="1">C42</f>
-        <v>7779629304.5622616</v>
+        <f>C42</f>
+        <v>8075054329.6707935</v>
       </c>
       <c r="D47" s="218"/>
       <c r="G47" s="219" t="s">
@@ -14687,8 +14687,8 @@
         <v>52</v>
       </c>
       <c r="C49" s="127">
-        <f ca="1">C47/C48</f>
-        <v>4.8622683153514137</v>
+        <f>C47/C48</f>
+        <v>5.0469089560442457</v>
       </c>
       <c r="D49" s="225"/>
       <c r="E49" s="194" t="s">
@@ -14701,11 +14701,11 @@
     </row>
     <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="201" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="C50" s="288">
-        <f ca="1">C49/C51</f>
-        <v>9.7245366307028278E-2</v>
+        <f>C49/C51</f>
+        <v>0.10093817912088492</v>
       </c>
       <c r="D50" s="225"/>
       <c r="E50" s="194" t="s">
@@ -14717,7 +14717,7 @@
     </row>
     <row r="51" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B51" s="201" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C51" s="127">
         <v>50</v>
@@ -14743,8 +14743,8 @@
         <v>55</v>
       </c>
       <c r="C53" s="111">
-        <f ca="1">(I19-$C$36)/(I21-$C$36)</f>
-        <v>0.65757022134026966</v>
+        <f>(I19-$C$36)/(I21-$C$36)</f>
+        <v>0.6605090550047813</v>
       </c>
       <c r="E53" s="227" t="s">
         <v>58</v>
@@ -14757,7 +14757,7 @@
     </row>
     <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="145" t="s">
-        <v>59</v>
+        <v>388</v>
       </c>
       <c r="C55" s="262"/>
       <c r="D55" s="262"/>
@@ -14769,8 +14769,8 @@
     </row>
     <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="C57" s="263">
-        <f ca="1">C49</f>
-        <v>4.8622683153514137</v>
+        <f>C49</f>
+        <v>5.0469089560442457</v>
       </c>
       <c r="D57" s="268">
         <f>E57-0.5%</f>
@@ -14798,20 +14798,20 @@
         <v>0.27189999999999998</v>
       </c>
       <c r="D58" s="267">
-        <f t="dataTable" ref="D58:H62" dt2D="1" dtr="1" r1="C36" r2="H4" ca="1"/>
-        <v>5.0253922522953465</v>
+        <f t="dataTable" ref="D58:H62" dt2D="1" dtr="1" r1="C36" r2="H4"/>
+        <v>5.2162299518771817</v>
       </c>
       <c r="E58" s="267">
-        <v>5.0253922522953465</v>
+        <v>5.2162299518771817</v>
       </c>
       <c r="F58" s="267">
-        <v>5.0253922522953465</v>
+        <v>5.2162299518771817</v>
       </c>
       <c r="G58" s="267">
-        <v>5.0253922522953465</v>
+        <v>5.2162299518771817</v>
       </c>
       <c r="H58" s="267">
-        <v>5.0253922522953465</v>
+        <v>5.2162299518771817</v>
       </c>
     </row>
     <row r="59" spans="2:10" x14ac:dyDescent="0.25">
@@ -14820,19 +14820,19 @@
         <v>0.27689999999999998</v>
       </c>
       <c r="D59" s="267">
-        <v>4.9429967174992351</v>
+        <v>5.130704221818978</v>
       </c>
       <c r="E59" s="267">
-        <v>4.9429967174992351</v>
+        <v>5.130704221818978</v>
       </c>
       <c r="F59" s="267">
-        <v>4.9429967174992351</v>
+        <v>5.130704221818978</v>
       </c>
       <c r="G59" s="267">
-        <v>4.9429967174992351</v>
+        <v>5.130704221818978</v>
       </c>
       <c r="H59" s="267">
-        <v>4.9429967174992351</v>
+        <v>5.130704221818978</v>
       </c>
     </row>
     <row r="60" spans="2:10" x14ac:dyDescent="0.25">
@@ -14840,19 +14840,19 @@
         <v>0.28189999999999998</v>
       </c>
       <c r="D60" s="267">
-        <v>4.8622683153514137</v>
+        <v>5.0469089560442457</v>
       </c>
       <c r="E60" s="267">
-        <v>4.8622683153514137</v>
+        <v>5.0469089560442457</v>
       </c>
       <c r="F60" s="267">
-        <v>4.8622683153514137</v>
+        <v>5.0469089560442457</v>
       </c>
       <c r="G60" s="267">
-        <v>4.8622683153514137</v>
+        <v>5.0469089560442457</v>
       </c>
       <c r="H60" s="267">
-        <v>4.8622683153514137</v>
+        <v>5.0469089560442457</v>
       </c>
     </row>
     <row r="61" spans="2:10" x14ac:dyDescent="0.25">
@@ -14861,19 +14861,19 @@
         <v>0.28689999999999999</v>
       </c>
       <c r="D61" s="267">
-        <v>4.7831670068067593</v>
+        <v>4.9648025945515597</v>
       </c>
       <c r="E61" s="267">
-        <v>4.7831670068067593</v>
+        <v>4.9648025945515597</v>
       </c>
       <c r="F61" s="267">
-        <v>4.7831670068067593</v>
+        <v>4.9648025945515597</v>
       </c>
       <c r="G61" s="267">
-        <v>4.7831670068067593</v>
+        <v>4.9648025945515597</v>
       </c>
       <c r="H61" s="267">
-        <v>4.7831670068067593</v>
+        <v>4.9648025945515597</v>
       </c>
     </row>
     <row r="62" spans="2:10" x14ac:dyDescent="0.25">
@@ -14882,19 +14882,19 @@
         <v>0.29189999999999999</v>
       </c>
       <c r="D62" s="267">
-        <v>4.7056538646885393</v>
+        <v>4.8843447314431421</v>
       </c>
       <c r="E62" s="267">
-        <v>4.7056538646885393</v>
+        <v>4.8843447314431421</v>
       </c>
       <c r="F62" s="267">
-        <v>4.7056538646885393</v>
+        <v>4.8843447314431421</v>
       </c>
       <c r="G62" s="267">
-        <v>4.7056538646885393</v>
+        <v>4.8843447314431421</v>
       </c>
       <c r="H62" s="267">
-        <v>4.7056538646885393</v>
+        <v>4.8843447314431421</v>
       </c>
     </row>
   </sheetData>
@@ -14959,7 +14959,7 @@
     </row>
     <row r="4" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="231" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="C4" s="232"/>
       <c r="D4" s="232"/>
@@ -14971,7 +14971,7 @@
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" s="172" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="C6" s="235">
         <v>0.2334</v>
@@ -14981,7 +14981,7 @@
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="172" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="C7" s="253">
         <f>IF(C21="Blume-adjusted",C24,C23)</f>
@@ -14990,7 +14990,7 @@
     </row>
     <row r="8" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="172" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="C8" s="236">
         <v>0.05</v>
@@ -14999,7 +14999,7 @@
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" s="237" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="C10" s="238">
         <f>C6+C7*C8</f>
@@ -15012,7 +15012,7 @@
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" s="38" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="C12" s="39"/>
       <c r="D12" s="39"/>
@@ -15021,7 +15021,7 @@
     </row>
     <row r="13" spans="2:9" x14ac:dyDescent="0.25">
       <c r="D13" s="112" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="E13" s="113"/>
       <c r="F13" s="112"/>
@@ -15061,7 +15061,7 @@
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B16" s="121" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="C16" s="118">
         <f>C17-0.005</f>
@@ -15079,7 +15079,7 @@
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="121" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="C17" s="122">
         <v>0.05</v>
@@ -15096,7 +15096,7 @@
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="121" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="C18" s="118">
         <f>C17+0.005</f>
@@ -15135,15 +15135,15 @@
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
+        <v>325</v>
+      </c>
+      <c r="C21" s="124" t="s">
         <v>326</v>
-      </c>
-      <c r="C21" s="124" t="s">
-        <v>327</v>
       </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="125" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="C23" s="126">
         <v>0.97</v>
@@ -15151,7 +15151,7 @@
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="125" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="C24" s="126">
         <f>2/3*C23+1/3</f>
@@ -15192,7 +15192,7 @@
     <row r="1" spans="2:9" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:9" s="241" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B2" s="239" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="C2" s="240"/>
     </row>
@@ -15201,7 +15201,7 @@
     </row>
     <row r="4" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B4" s="44" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="C4" s="144">
         <v>46307</v>
@@ -15210,7 +15210,7 @@
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B6" s="145" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="C6" s="146"/>
       <c r="D6" s="146"/>
@@ -15220,67 +15220,67 @@
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B7" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="C7" s="242" t="s">
+        <v>332</v>
+      </c>
+      <c r="D7" s="242" t="s">
+        <v>333</v>
+      </c>
+      <c r="E7" s="242" t="s">
+        <v>334</v>
+      </c>
+      <c r="F7" s="242" t="s">
+        <v>335</v>
+      </c>
+      <c r="G7" s="242" t="s">
         <v>62</v>
-      </c>
-      <c r="C7" s="242" t="s">
-        <v>333</v>
-      </c>
-      <c r="D7" s="242" t="s">
-        <v>334</v>
-      </c>
-      <c r="E7" s="242" t="s">
-        <v>335</v>
-      </c>
-      <c r="F7" s="242" t="s">
-        <v>336</v>
-      </c>
-      <c r="G7" s="242" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B8" s="35" t="s">
+        <v>336</v>
+      </c>
+      <c r="C8" s="243" t="s">
         <v>337</v>
       </c>
-      <c r="C8" s="243" t="s">
+      <c r="D8" s="243" t="s">
         <v>338</v>
       </c>
-      <c r="D8" s="243" t="s">
+      <c r="E8" s="243" t="s">
         <v>339</v>
       </c>
-      <c r="E8" s="243" t="s">
+      <c r="F8" s="243" t="s">
         <v>340</v>
       </c>
-      <c r="F8" s="243" t="s">
+      <c r="G8" s="243" t="s">
         <v>341</v>
-      </c>
-      <c r="G8" s="243" t="s">
-        <v>342</v>
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B9" s="35" t="s">
+        <v>342</v>
+      </c>
+      <c r="C9" s="242" t="s">
         <v>343</v>
       </c>
-      <c r="C9" s="242" t="s">
-        <v>344</v>
-      </c>
       <c r="D9" s="242" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E9" s="242" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="F9" s="242" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="G9" s="242" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B10" s="35" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="C10" s="144">
         <v>46022</v>
@@ -15300,7 +15300,7 @@
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B11" s="35" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="C11" s="253">
         <v>18.7</v>
@@ -15321,7 +15321,7 @@
     </row>
     <row r="12" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B12" s="244" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="C12" s="245">
         <f>$C$4</f>
@@ -15348,7 +15348,7 @@
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B14" s="145" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="C14" s="146"/>
       <c r="D14" s="146"/>
@@ -15358,7 +15358,7 @@
     </row>
     <row r="15" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B15" s="35" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="C15" s="246">
         <v>3406523244</v>
@@ -15379,7 +15379,7 @@
     </row>
     <row r="16" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B16" s="35" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="C16" s="252">
         <v>0</v>
@@ -15401,7 +15401,7 @@
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B17" s="44" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C17" s="148">
         <f>SUM(C15:C16)</f>
@@ -15426,7 +15426,7 @@
     </row>
     <row r="19" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B19" s="145" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="C19" s="146"/>
       <c r="D19" s="146"/>
@@ -15436,7 +15436,7 @@
     </row>
     <row r="20" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B20" s="35" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="C20" s="250">
         <f>C17*C11</f>
@@ -15461,7 +15461,7 @@
     </row>
     <row r="22" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B22" s="145" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C22" s="146"/>
       <c r="D22" s="146"/>
@@ -15471,7 +15471,7 @@
     </row>
     <row r="23" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B23" s="35" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C23" s="251">
         <v>2889189159</v>
@@ -15492,7 +15492,7 @@
     </row>
     <row r="24" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B24" s="35" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C24" s="251">
         <v>7730539324</v>
@@ -15513,7 +15513,7 @@
     </row>
     <row r="25" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B25" s="35" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C25" s="252">
         <v>-91606292</v>
@@ -15534,7 +15534,7 @@
     </row>
     <row r="26" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B26" s="35" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C26" s="252">
         <v>-1488621582</v>
@@ -15555,7 +15555,7 @@
     </row>
     <row r="27" spans="2:7" s="35" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B27" s="35" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C27" s="151">
         <f>SUM(C24:C26)</f>
@@ -15580,7 +15580,7 @@
     </row>
     <row r="29" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B29" s="145" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C29" s="146"/>
       <c r="D29" s="146"/>
@@ -15590,7 +15590,7 @@
     </row>
     <row r="30" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B30" s="44" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="C30" s="150">
         <f>C20/C23</f>
@@ -15615,7 +15615,7 @@
     </row>
     <row r="31" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B31" s="44" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="C31" s="150">
         <f>C20/C24</f>
@@ -15640,7 +15640,7 @@
     </row>
     <row r="32" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B32" s="44" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="C32" s="150">
         <f>C20/C27</f>
@@ -15665,7 +15665,7 @@
     </row>
     <row r="33" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B33" s="44" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="C33" s="247">
         <f>C23/C24</f>
@@ -15690,7 +15690,7 @@
     </row>
     <row r="35" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B35" s="145" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C35" s="146"/>
       <c r="D35" s="146"/>
@@ -15700,16 +15700,16 @@
     </row>
     <row r="36" spans="2:7" x14ac:dyDescent="0.25">
       <c r="C36" s="44" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="D36" s="44" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="F36" s="44" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="G36" s="44"/>
     </row>
@@ -15722,7 +15722,7 @@
     </row>
     <row r="38" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B38" s="35" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="C38" s="149">
         <f>AVERAGE(C30:F30)</f>
@@ -15744,7 +15744,7 @@
     </row>
     <row r="39" spans="2:7" s="13" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B39" s="44" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="C39" s="150">
         <f>MEDIAN(C30:F30)</f>
@@ -15766,7 +15766,7 @@
     </row>
     <row r="40" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B40" s="35" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="C40" s="149">
         <f>MAX(C30:F30)</f>
@@ -15788,7 +15788,7 @@
     </row>
     <row r="41" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B41" s="35" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C41" s="149">
         <f>MIN(C30:F30)</f>
@@ -15810,7 +15810,7 @@
     </row>
     <row r="43" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B43" s="145" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="C43" s="146"/>
       <c r="D43" s="146"/>
@@ -15820,12 +15820,12 @@
     </row>
     <row r="44" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B44" s="44" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="45" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B45" s="35" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="C45" s="149">
         <f>C39</f>
@@ -15834,7 +15834,7 @@
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B46" s="35" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C46" s="151">
         <f>$G$23</f>
@@ -15843,7 +15843,7 @@
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B47" s="35" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C47" s="151">
         <f>C45*C46</f>
@@ -15852,7 +15852,7 @@
     </row>
     <row r="48" spans="2:7" x14ac:dyDescent="0.25">
       <c r="B48" s="35" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C48" s="248">
         <f>$G$15</f>
@@ -15861,7 +15861,7 @@
     </row>
     <row r="49" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B49" s="44" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C49" s="249">
         <f>C47/C48</f>
@@ -15870,12 +15870,12 @@
     </row>
     <row r="51" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B51" s="44" t="s">
-        <v>376</v>
+        <v>390</v>
       </c>
     </row>
     <row r="52" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B52" s="35" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C52" s="149">
         <f>D39</f>
@@ -15884,7 +15884,7 @@
     </row>
     <row r="53" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B53" s="35" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="C53" s="151">
         <f>G24</f>
@@ -15893,7 +15893,7 @@
     </row>
     <row r="54" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B54" s="35" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C54" s="151">
         <f>C52*C53</f>
@@ -15902,7 +15902,7 @@
     </row>
     <row r="55" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B55" s="35" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C55" s="248">
         <f>C48</f>
@@ -15911,7 +15911,7 @@
     </row>
     <row r="56" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B56" s="44" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C56" s="249">
         <f>C54/C55</f>
@@ -15924,12 +15924,12 @@
     </row>
     <row r="58" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B58" s="44" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
     </row>
     <row r="59" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B59" s="35" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="C59" s="149">
         <f>E39</f>
@@ -15938,7 +15938,7 @@
     </row>
     <row r="60" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B60" s="35" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C60" s="151">
         <f>G27</f>
@@ -15947,7 +15947,7 @@
     </row>
     <row r="61" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B61" s="35" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C61" s="151">
         <f>C59*C60</f>
@@ -15956,7 +15956,7 @@
     </row>
     <row r="62" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B62" s="35" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C62" s="248">
         <f>C55</f>
@@ -15965,7 +15965,7 @@
     </row>
     <row r="63" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B63" s="44" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C63" s="249">
         <f>C61/C62</f>
@@ -15974,12 +15974,12 @@
     </row>
     <row r="65" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B65" s="44" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="66" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B66" s="35" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="C66" s="149">
         <f>MEDIAN(E30:F30)</f>
@@ -15988,7 +15988,7 @@
     </row>
     <row r="67" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B67" s="35" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="C67" s="151">
         <f>G23</f>
@@ -15997,7 +15997,7 @@
     </row>
     <row r="68" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B68" s="35" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C68" s="151">
         <f>C66*C67</f>
@@ -16006,7 +16006,7 @@
     </row>
     <row r="69" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B69" s="35" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="C69" s="248">
         <f>C62</f>
@@ -16015,7 +16015,7 @@
     </row>
     <row r="70" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B70" s="44" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="C70" s="249">
         <f>C68/C69</f>
